--- a/data_extactor/batch/601_650.xlsx
+++ b/data_extactor/batch/601_650.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2321AF59-45CF-4E3D-8D10-79074BBAF387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1633 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="540">
+  <si>
+    <t>39-4021.00</t>
+  </si>
+  <si>
+    <t>Funeral Attendants</t>
+  </si>
+  <si>
+    <t>Funeral Assistant | Funeral Associate | Funeral Attendant | Funeral Director | Funeral Greeter | Funeral Home Assistant | Funeral Home Associate | Funeral Home Attendant</t>
+  </si>
+  <si>
+    <t>Bookkeeping software | Microsoft Excel | Microsoft Office software | Microsoft Word | iCIMS Talent Cloud software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Near Vision | Speech Recognition | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Telephone Conversations | Time Pressure | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Baggage Porters and Bellhops | Concierges | Coroners | Crematory Operators | Embalmers | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Personal Service Workers | Funeral Home Managers | Home Health Aides | Maids and Housekeeping Cleaners | Morticians, Undertakers, and Funeral Arrangers | Nursing Assistants | Orderlies | Passenger Attendants | Personal Care Aides | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Stockers and Order Fillers | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Perform a variety of tasks during funeral, such as placing casket in parlor or chapel prior to service, arranging floral offerings or lights around casket, directing or escorting mourners, closing casket, and issuing and storing funeral equipment.</t>
+  </si>
+  <si>
+    <t>Act as pallbearers. | Arrange floral offerings or lights around caskets. | Assist with cremations and the processing and packaging of cremated remains. | Attend to the needs of the bereaved, such as by offering comfort, counseling, or after-care programs. | Carry flowers to hearses or limousines for transportation to places of interment. | Clean and drive funeral vehicles, such as cars or hearses, in funeral processions. | Clean funeral parlors or chapels. | Close caskets at appropriate point in services. | Deliver floral arrangements or other items to family members of the deceased. | Direct or escort mourners to parlors or chapels in which wakes or funerals are being held. | Embalm, dress, cosmeticize, and casket the deceased. | Greet people at the funeral home. | Issue and store funeral equipment. | Obtain burial permits and register deaths. | Obtain doctors' signatures on death certificate and complete other paperwork, such as insurance claims forms. | Offer assistance to mourners as they enter or exit limousines. | Perform a variety of tasks during funerals to assist funeral directors and to ensure that services run smoothly and as planned. | Perform general maintenance tasks for funeral homes, such as maintaining equipment or caring for funeral grounds. | Perform various administrative tasks, such as typing documents or answering telephone calls. | Place caskets in parlors or chapels prior to wakes or funerals. | Prepare obituaries for newspapers. | Provide advice to mourners on how to make charitable donations in honor of the deceased. | Supervise funeral processions and assist with cemetery parking. | Transport the deceased to the funeral home.</t>
+  </si>
+  <si>
+    <t>39-4031.00</t>
+  </si>
+  <si>
+    <t>Morticians, Undertakers, and Funeral Arrangers</t>
+  </si>
+  <si>
+    <t>Funeral Arrangement Director | Funeral Arranger | Funeral Counselor | Funeral Director | Funeral Family Service Assistant | Funeral Location Manager | Funeral Prearrangement Counselor | Licensed Funeral Director | Licensed Mortician | Mortician</t>
+  </si>
+  <si>
+    <t>Belmar &amp; Associates Mortware | Corel WordPerfect Office Suite | Custom Data Systems Sterling Management Software | FPA Software MACCS | FuneralKiosk | HMIS Advantage | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Salesforce software | Twin Tier Technologies MIMS | Web browser software | iCIMS Talent Cloud software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Writing | Reading Comprehension | Critical Thinking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Administration and Management | Psychology | Personnel and Human Resources | Computers and Electronics | Sales and Marketing | Biology | Philosophy and Theology | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Problem Sensitivity | Information Ordering | Near Vision | Selective Attention | Deductive Reasoning | Fluency of Ideas | Written Expression | Written Comprehension | Category Flexibility | Inductive Reasoning | Originality</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Contaminants | Work Outcomes and Results of Other Workers | Physical Proximity | Health and Safety of Other Workers | Time Pressure | Written Letters and Memos | E-Mail</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Clergy | Coroners | Crematory Operators | Directors, Religious Activities and Education | Embalmers | First-Line Supervisors of Personal Service Workers | Funeral Attendants | Funeral Home Managers | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Medical and Health Services Managers | Nursing Assistants | Patient Representatives | Personal Care Aides | Rehabilitation Counselors | Residential Advisors | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Social and Community Service Managers | Social and Human Service Assistants</t>
+  </si>
+  <si>
+    <t>Perform various tasks to arrange and direct individual funeral services, such as coordinating transportation of body to mortuary, interviewing family or other authorized person to arrange details, selecting pallbearers, aiding with the selection of officials for religious rites, and providing transportation for mourners.</t>
+  </si>
+  <si>
+    <t>Arrange for clergy members to perform needed services. | Arrange for pallbearers or inform pallbearers or honorary groups of their duties. | Clean funeral home facilities and grounds. | Close caskets and lead funeral corteges to churches or burial sites. | Consult with families or friends of the deceased to arrange funeral details, such as obituary notice wording, casket selection, or plans for services. | Contact cemeteries to schedule the opening and closing of graves. | Direct preparations and shipment of bodies for out-of-state burial. | Discuss and negotiate prearranged funerals with clients. | Inform survivors of benefits for which they may be eligible. | Maintain financial records, order merchandise, or prepare accounts. | Manage funeral home operations, including the hiring, training, or supervision of embalmers, funeral attendants, or other staff. | Obtain information needed to complete legal documents, such as death certificates or burial permits. | Offer counsel and comfort to bereaved families or friends. | Oversee the preparation and care of the remains of people who have died. | Participate in community activities for funeral home promotion or other purposes. | Perform embalming duties, as necessary. | Plan placement of caskets at funeral sites or place or adjust lights, fixtures, or floral displays. | Plan, schedule, or coordinate funerals, burials, or cremations, arranging details such as floral delivery or the time and place of services. | Provide information on funeral service options, products, or merchandise, and maintain a casket display area. | Provide or arrange transportation between sites for the remains, mourners, pallbearers, clergy, or flowers. | Receive or usher people to their seats for services. | Remove deceased remains from place of death.</t>
+  </si>
+  <si>
+    <t>39-5011.00</t>
+  </si>
+  <si>
+    <t>Barbers</t>
+  </si>
+  <si>
+    <t>Barber | Barber Shop Operator | Barber Stylist | Stylist</t>
+  </si>
+  <si>
+    <t>Appointment scheduling software | Customer information databases | Facebook | Linux | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Point of sale POS payment software | YouTube</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | English Language | Economics and Accounting | Psychology</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Oral Comprehension | Near Vision | Finger Dexterity | Manual Dexterity | Oral Expression | Speech Recognition | Speech Clarity | Selective Attention | Trunk Strength | Control Precision | Visualization | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Freedom to Make Decisions | Physical Proximity | Spend Time Standing | Telephone Conversations | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Level of Competition | Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Personal Service Workers | Floral Designers | Furniture Finishers | Hairdressers, Hairstylists, and Cosmetologists | Jewelers and Precious Stone and Metal Workers | Laundry and Dry-Cleaning Workers | Locker Room, Coatroom, and Dressing Room Attendants | Maids and Housekeeping Cleaners | Makeup Artists, Theatrical and Performance | Manicurists and Pedicurists | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Retail Salespersons | Sewers, Hand | Shampooers | Shoe and Leather Workers and Repairers | Skincare Specialists | Spa Managers | Tailors, Dressmakers, and Custom Sewers</t>
+  </si>
+  <si>
+    <t>Provide barbering services, such as cutting, trimming, shampooing, and styling hair; trimming beards; or giving shaves.</t>
+  </si>
+  <si>
+    <t>Apply lather and shave beards or neck and temple hair contours, using razors. | Clean and sterilize scissors, combs, clippers, and other instruments. | Clean work stations and sweep floors. | Curl, color, or straighten hair, using special chemical solutions and equipment. | Cut and trim hair according to clients' instructions or current hairstyles, using clippers, combs, hand-held blow driers, and scissors. | Drape and pin protective cloths around customers' shoulders. | Keep card files on clientele, recording notes of work done, products used and fees charged after each visit. | Order supplies. | Perform clerical and administrative duties such as keeping records, paying bills, and hiring and supervising personnel. | Provide face, neck, and scalp massages. | Provide skin care and nail treatments. | Question patrons regarding desired services and haircut styles. | Recommend and sell lotions, tonics, or other cosmetic supplies. | Record services provided on cashiers' tickets or receive payment from customers. | Shampoo hair. | Shape and trim beards and moustaches, using scissors. | Stay informed of the latest styles and hair care techniques. | Suggest treatments to alleviate hair problems.</t>
+  </si>
+  <si>
+    <t>39-5012.00</t>
+  </si>
+  <si>
+    <t>Hairdressers, Hairstylists, and Cosmetologists</t>
+  </si>
+  <si>
+    <t>Beautician | Cosmetologist | Hair Dresser | Hair Stylist | Hairdresser | Hairstylist | Stylist</t>
+  </si>
+  <si>
+    <t>Apple iOS | Appointment scheduling software | Customer information databases | Facebook | Intuit QuickBooks | Microsoft Excel | Microsoft Office software | Microsoft Word | Sale processing software | YouTube</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Active Learning | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | Administration and Management</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Oral Comprehension | Originality | Oral Expression | Speech Recognition | Visualization | Fluency of Ideas | Speech Clarity | Visual Color Discrimination | Problem Sensitivity | Selective Attention | Category Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Physical Proximity | Spend Time Standing | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Level of Competition | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Barbers | Costume Attendants | Fashion Designers | Floral Designers | Furniture Finishers | Jewelers and Precious Stone and Metal Workers | Laundry and Dry-Cleaning Workers | Maids and Housekeeping Cleaners | Makeup Artists, Theatrical and Performance | Manicurists and Pedicurists | Opticians, Dispensing | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Retail Salespersons | Sewers, Hand | Shampooers | Shoe and Leather Workers and Repairers | Skincare Specialists | Spa Managers | Tailors, Dressmakers, and Custom Sewers</t>
+  </si>
+  <si>
+    <t>Provide beauty services, such as cutting, coloring, and styling hair, and massaging and treating scalp. May shampoo hair, apply makeup, dress wigs, remove hair, and provide nail and skincare services.</t>
+  </si>
+  <si>
+    <t>Administer therapeutic medication and advise patron to seek medical treatment for chronic or contagious scalp conditions. | Analyze patrons' hair and other physical features to determine and recommend beauty treatment or suggest hair styles. | Apply water or setting, straightening or waving solutions to hair, and use curlers, rollers, hot combs and curling irons to press and curl hair. | Attach wigs or hairpieces to model heads and dress wigs and hairpieces according to instructions, samples, sketches or photographs. | Bleach, dye, or tint hair, using applicator or brush. | Clean, shape, and polish fingernails and toenails, using files and nail polish. | Comb, brush, and spray hair or wigs to set style. | Cut, trim and shape hair or hairpieces, based on customers' instructions, hair type, and facial features, using clippers, scissors, trimmers and razors. | Demonstrate and sell hair care products and cosmetics. | Develop new styles and techniques. | Give facials to patrons, using special compounds, such as lotions and creams. | Keep work stations clean and sanitize tools, such as scissors and combs. | Massage and treat scalp for hygienic and remedial purposes, using hands, fingers, or vibrating equipment. | Operate cash registers to receive payments from patrons. | Order, display, and maintain supplies. | Recommend and explain the use of cosmetics, lotions, and creams to soften and lubricate skin and enhance and restore natural appearance. | Schedule client appointments. | Shampoo, rinse, condition, and dry hair and scalp or hairpieces with water, liquid soap, or other solutions. | Shape eyebrows and remove facial hair, using depilatory cream, tweezers, electrolysis or wax. | Shave, trim, and shape beards and moustaches. | Train or supervise other hairstylists, hairdressers, and assistants. | Update and maintain customer information records, such as beauty services provided.</t>
+  </si>
+  <si>
+    <t>39-5091.00</t>
+  </si>
+  <si>
+    <t>Makeup Artists, Theatrical and Performance</t>
+  </si>
+  <si>
+    <t>Commercial Makeup Artist (Commercial MUA) | Hair and Makeup Designer | Makeup Artist (MUA) | Prosthetic Makeup Designer | Special Effects Makeup Artist (Special Effects MUA) | Special Makeup Effects Artist | TV and Film Makeup Artist (Television and Film Makeup Artist)</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Appointment scheduling software | Autodesk Maya | Autodesk Mudbox | Blogging software | Bookitlive | Clear Books | Client databases | DatInf DigiMakeup | Email software | Facebook | Instagram | Intuit QuickBooks | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Pixologic Zbrush | SavingFace | Twitter | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Reading Comprehension | Active Listening | Critical Thinking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Fine Arts | Design | Communications and Media</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Visual Color Discrimination | Oral Expression | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Visualization | Originality | Fluency of Ideas | Written Comprehension | Speech Recognition | Problem Sensitivity | Selective Attention | Information Ordering | Category Flexibility | Deductive Reasoning | Speech Clarity | Far Vision | Written Expression | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Physical Proximity | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Contact With Others | Work With or Contribute to a Work Group or Team | Time Pressure | Health and Safety of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Level of Competition | Indoors, Environmentally Controlled | Telephone Conversations | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Spend Time Standing | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Outdoors, Exposed to All Weather Conditions | Exposed to Extremely Bright or Inadequate Lighting Conditions | Outdoors, Under Cover | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Barbers | Costume Attendants | Craft Artists | Etchers and Engravers | Fashion Designers | Fine Artists, Including Painters, Sculptors, and Illustrators | Floral Designers | Graphic Designers | Hairdressers, Hairstylists, and Cosmetologists | Jewelers and Precious Stone and Metal Workers | Manicurists and Pedicurists | Models | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Photographers | Sewers, Hand | Shampooers | Skincare Specialists | Special Effects Artists and Animators | Tailors, Dressmakers, and Custom Sewers</t>
+  </si>
+  <si>
+    <t>Apply makeup to performers to reflect period, setting, and situation of their role.</t>
+  </si>
+  <si>
+    <t>Advise hairdressers on the hairstyles required for character parts. | Alter or maintain makeup during productions as necessary to compensate for lighting changes or to achieve continuity of effect. | Analyze a script, noting events that affect each character's appearance, so that plans can be made for each scene. | Apply makeup to enhance or alter the appearance of people appearing in productions such as movies. | Assess performers' skin type to ensure that makeup will not cause break-outs or skin irritations. | Attach prostheses to performers and apply makeup to create special features or effects, such as scars, aging, or illness. | Clean supplies such as makeup brushes. | Cleanse and tone the skin to prepare it for makeup application. | Confer with stage or motion picture officials and performers to determine desired effects. | Create character drawings or models, based upon independent research, to augment period production files. | Demonstrate products to clients, and provide instruction in makeup application. | Design rubber or plastic prostheses that can be used to change performers' appearances. | Duplicate work precisely to replicate characters' appearances on a daily basis. | Establish budgets, and work within budgetary limits. | Evaluate environmental characteristics, such as venue size and lighting plans, to determine makeup requirements. | Examine sketches, photographs, and plaster models to obtain desired character image depiction. | Provide performers with makeup removal assistance after performances have been completed. | Requisition or acquire needed materials for special effects, including wigs, beards, and special cosmetics. | Select desired makeup shades from stock, or mix oil, grease, and coloring to achieve specific color effects. | Study production information, such as character descriptions, period settings, and situations, to determine makeup requirements. | Wash and reset wigs. | Write makeup sheets and take photos to document specific looks and the products used to achieve the looks.</t>
+  </si>
+  <si>
+    <t>39-5092.00</t>
+  </si>
+  <si>
+    <t>Manicurists and Pedicurists</t>
+  </si>
+  <si>
+    <t>Manicurist | Nail Technician (Nail Tech) | Pedicurist</t>
+  </si>
+  <si>
+    <t>Aknaf ADVANTAGE Salon Software and Spa Software | Appointment Search | AppointmentQuest Online Appointment Scheduler | Customer information databases | DaySmart Software Appointment-Plus | DaySmart Software Salon Iris | Facebook | Microsoft Excel | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Near Vision | Finger Dexterity | Arm-Hand Steadiness | Speech Recognition | Manual Dexterity | Oral Expression</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Physical Proximity | Spend Time Making Repetitive Motions | Contact With Others | Indoors, Environmentally Controlled | Spend Time Sitting | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Barbers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Dental Laboratory Technicians | Etchers and Engravers | Foundry Mold and Coremakers | Furniture Finishers | Grinding and Polishing Workers, Hand | Hairdressers, Hairstylists, and Cosmetologists | Laundry and Dry-Cleaning Workers | Makeup Artists, Theatrical and Performance | Molders, Shapers, and Casters, Except Metal and Plastic | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Sewers, Hand | Shampooers | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Skincare Specialists | Tool Grinders, Filers, and Sharpeners</t>
+  </si>
+  <si>
+    <t>Clean and shape customers' fingernails and toenails. May polish or decorate nails.</t>
+  </si>
+  <si>
+    <t>Advise clients on nail care and use of products and colors. | Apply undercoat and clear or colored polish onto nails with brush. | Assess the condition of clients' hands, remove dead skin, and massage hands. | Clean and sanitize tools and work environment. | Decorate clients' nails by piercing or attaching ornaments or designs. | Extend nails using powder, solvent, and paper forms attached to tips of customers' fingers to support and shape artificial nails. | Maintain supply inventories and records of client services. | Polish nails, using powdered polish and buffer. | Prepare customers' nails in soapy water, using swabs, files, and orange sticks. | Prepare nail cuticles with water and oil, using cuticle knives to push back cuticles and scissors or nippers to trim cuticles. | Promote and sell nail care products. | Remove previously applied nail polish, using liquid remover and swabs. | Roughen surfaces of fingernails, using abrasive wheel. | Schedule client appointments and accept payments. | Shape and smooth ends of nails, using scissors, files, or emery boards. | Treat nails to repair or improve strength and resilience by wrapping. | Use rotary abrasive wheels to shape and smooth nails or artificial extensions. | Whiten underside of nails with white paste or pencils.</t>
+  </si>
+  <si>
+    <t>39-5093.00</t>
+  </si>
+  <si>
+    <t>Shampooers</t>
+  </si>
+  <si>
+    <t>Hair Assistant | Shampoo Assistant | Shampoo Person | Shampoo Technician | Shampooer | Stylist Assistant</t>
+  </si>
+  <si>
+    <t>Appointment scheduling software | Email software | Facebook | Inventory tracking software | Web browser software</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Near Vision | Arm-Hand Steadiness | Manual Dexterity</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Contact With Others | Spend Time Standing | Importance of Being Exact or Accurate | Physical Proximity | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Deal With External Customers or the Public in General | Telephone Conversations | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Acupuncturists | Barbers | Dental Assistants | Dental Hygienists | Dentists, General | Emergency Medicine Physicians | Hairdressers, Hairstylists, and Cosmetologists | Home Health Aides | Laundry and Dry-Cleaning Workers | Makeup Artists, Theatrical and Performance | Manicurists and Pedicurists | Massage Therapists | Nursing Assistants | Oral and Maxillofacial Surgeons | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Physical Therapist Aides | Skincare Specialists | Surgical Assistants | Veterinary Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Shampoo and rinse customers' hair.</t>
+  </si>
+  <si>
+    <t>Advise patrons with chronic or potentially contagious scalp conditions to seek medical treatment. | Maintain treatment records. | Massage, shampoo, and condition patron's hair and scalp to clean them and remove excess oil. | Treat scalp conditions and hair loss, using specialized lotions, shampoos, or equipment such as infrared lamps or vibrating equipment.</t>
+  </si>
+  <si>
+    <t>39-5094.00</t>
+  </si>
+  <si>
+    <t>Skincare Specialists</t>
+  </si>
+  <si>
+    <t>Aesthetician | Clinical Esthetician | Electrologist | Esthetician | Facialist | Medical Esthetician | Skin Therapist | Skincare Specialist | Skincare Therapist | Spa Technician (Spa Tech)</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Spa management software | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Reading Comprehension | Critical Thinking | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | Administration and Management | Education and Training | English Language | Administrative | Communications and Media</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Oral Expression | Speech Recognition | Deductive Reasoning | Speech Clarity | Written Comprehension | Problem Sensitivity | Arm-Hand Steadiness | Finger Dexterity | Selective Attention | Manual Dexterity | Category Flexibility | Information Ordering | Inductive Reasoning | Fluency of Ideas | Written Expression</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Indoors, Environmentally Controlled | Frequency of Decision Making | Physical Proximity | Deal With External Customers or the Public in General | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Exposed to Disease or Infections | Level of Competition</t>
+  </si>
+  <si>
+    <t>Acupuncturists | Barbers | Dental Assistants | Dentists, General | Dermatologists | Hairdressers, Hairstylists, and Cosmetologists | Makeup Artists, Theatrical and Performance | Manicurists and Pedicurists | Massage Therapists | Medical Assistants | Optometrists | Oral and Maxillofacial Surgeons | Pediatric Surgeons | Physical Therapist Aides | Podiatrists | Prosthodontists | Shampooers | Spa Managers | Surgical Assistants | Surgical Technologists</t>
+  </si>
+  <si>
+    <t>Provide skincare treatments to face and body to enhance an individual's appearance. Includes electrologists and laser hair removal specialists.</t>
+  </si>
+  <si>
+    <t>Advise clients about colors and types of makeup and instruct them in makeup application techniques. | Apply chemical peels to reduce fine lines and age spots. | Cleanse clients' skin with water, creams, or lotions. | Collaborate with plastic surgeons and dermatologists to provide patients with preoperative and postoperative skin care. | Demonstrate how to clean and care for skin properly and recommend skin-care regimens. | Determine which products or colors will improve clients' skin quality and appearance. | Examine clients' skin, using magnifying lamps or visors when necessary, to evaluate skin condition and appearance. | Keep records of client needs and preferences and the services provided. | Perform simple extractions to remove blackheads. | Provide facial and body massages. | Refer clients to medical personnel for treatment of serious skin problems. | Remove body and facial hair by applying wax. | Select and apply cosmetic products, such as creams, lotions, and tonics. | Sell makeup to clients. | Stay abreast of latest industry trends, products, research, and treatments. | Sterilize equipment and clean work areas. | Tint eyelashes and eyebrows. | Treat the facial skin to maintain and improve its appearance, using specialized techniques and products, such as peels and masks.</t>
+  </si>
+  <si>
+    <t>39-6011.00</t>
+  </si>
+  <si>
+    <t>Baggage Porters and Bellhops</t>
+  </si>
+  <si>
+    <t>Bell Captain | Bell Person | Bellhop | Bellman | Bellperson | Doorman | Ground Support Agent | Sky Cap | Skycap | Valet</t>
+  </si>
+  <si>
+    <t>Corel WordPerfect Office Suite | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Public Safety and Security | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Trunk Strength | Speech Recognition | Static Strength | Multilimb Coordination | Speech Clarity | Extent Flexibility | Stamina | Time Sharing | Selective Attention | Problem Sensitivity | Near Vision</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Indoors, Environmentally Controlled | Contact With Others | Deal With External Customers or the Public in General | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Telephone Conversations | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Walking or Running | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Dealing With Unpleasant, Angry, or Discourteous People | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Amusement and Recreation Attendants | Bus Drivers, Transit and Intercity | Cashiers | Concierges | Counter and Rental Clerks | Couriers and Messengers | Dining Room and Cafeteria Attendants and Bartender Helpers | Dispatchers, Except Police, Fire, and Ambulance | Flight Attendants | Food Servers, Nonrestaurant | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants | Parking Attendants | Passenger Attendants | Reservation and Transportation Ticket Agents and Travel Clerks | Shuttle Drivers and Chauffeurs | Stockers and Order Fillers | Transportation Security Screeners | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Handle baggage for travelers at transportation terminals or for guests at hotels or similar establishments.</t>
+  </si>
+  <si>
+    <t>Act as part of the security team at transportation terminals, hotels, or similar establishments. | Arrange for shipments of baggage, express mail, and parcels by providing weighing and billing services. | Assist travelers and guests with disabilities. | Complete baggage insurance forms. | Compute and complete charge slips for services rendered and maintain records. | Deliver messages and room service orders, and run errands for guests. | Explain the operation of room features, such as locks, ventilation systems, and televisions. | Greet incoming guests and escort them to their rooms. | Inspect guests' rooms to ensure that they are adequately stocked, orderly, and comfortable. | Maintain clean lobbies or entrance areas for travelers or guests. | Page guests in hotel lobbies, dining rooms, or other areas. | Pick up and return items for laundry and valet service. | Receive and mark baggage by completing and attaching claim checks. | Set up conference rooms, display tables, racks, or shelves, and arrange merchandise displays for sales personnel. | Supply guests or travelers with directions, travel information, and other information, such as available services and points of interest. | Transfer luggage, trunks, and packages to and from rooms, loading areas, vehicles, or transportation terminals, by hand or using baggage carts. | Transport guests about premises and local areas, or arrange for transportation.</t>
+  </si>
+  <si>
+    <t>39-6012.00</t>
+  </si>
+  <si>
+    <t>Concierges</t>
+  </si>
+  <si>
+    <t>Activities Concierge | Chef Concierge | Club Concierge | Concierge | Conference Concierge | Front Desk Agent | Guest Service Agent | Hotel Concierge | Lobby Concierge | Service Concierge</t>
+  </si>
+  <si>
+    <t>Billing software | Budgeting software | Delphi Technology | Mapping software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Web browser software | Work scheduling software | Yardi software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Deductive Reasoning | Problem Sensitivity | Information Ordering | Originality | Fluency of Ideas | Written Expression | Written Comprehension | Near Vision | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Time Pressure | Written Letters and Memos | Importance of Being Exact or Accurate | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Baggage Porters and Bellhops | Counter and Rental Clerks | Customer Service Representatives | Dining Room and Cafeteria Attendants and Bartender Helpers | Flight Attendants | Food Servers, Nonrestaurant | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants | Lodging Managers | Maids and Housekeeping Cleaners | Meeting, Convention, and Event Planners | Parking Attendants | Passenger Attendants | Receptionists and Information Clerks | Reservation and Transportation Ticket Agents and Travel Clerks | Travel Agents | Travel Guides | Ushers, Lobby Attendants, and Ticket Takers | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Assist patrons at hotel, apartment, or office building with personal services. May take messages; arrange or give advice on transportation, business services, or entertainment; or monitor guest requests for housekeeping and maintenance.</t>
+  </si>
+  <si>
+    <t>Arrange childcare services for guests. | Arrange for interpreters or translators when patrons require such services. | Arrange for the replacement of items lost by travelers. | Assist guests with special needs by providing equipment such as wheelchairs. | Book airline or train tickets, reserve rental cars, or arrange shuttle service for guests. | Carry out unusual requests, such as searching for hard-to-find items or arranging for exotic services, such as hot-air balloon rides. | Clean and tidy hotel lounge. | Make reservations for patrons, such as for dinner, spa treatments, or golf tee times, and obtain tickets to special events. | Make travel arrangements for sightseeing or other tours. | Order flowers for guests. | Perform office duties on a temporary basis when needed. | Pick up and deliver items or run errands for guests. | Plan special events, parties, or meetings, which may include booking musicians or celebrities. | Provide business services for guests, such as sending or receiving faxes or shipping packages. | Provide directions to guests. | Provide food and beverage services to guests. | Provide information about local features, such as shopping, dining, nightlife, or recreational destinations. | Receive, store, or deliver luggage or mail.</t>
+  </si>
+  <si>
+    <t>39-7011.00</t>
+  </si>
+  <si>
+    <t>Tour Guides and Escorts</t>
+  </si>
+  <si>
+    <t>Art Museum Docent | Discovery Guide | Docent | Guide | Historical Interpreter | Museum Docent | Museum Educator | Museum Guide | Science Interpreter | Tour Guide</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Apple Safari | Centaur Systems Centaur Travel Business Management System TBMS | Email software | Facebook | Global positioning system GPS software | IBS Software Services Tour Partner | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | Pear Deck | RBS GoTour Online | SmugMug Flickr | Softrip Travel Software System | TourTech Systems TourTools | Zoom</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | History and Archeology | Communications and Media | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Clarity | Speech Recognition | Written Comprehension | Far Vision | Near Vision | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Public Speaking | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Physical Proximity | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Spend Time Standing | Frequency of Decision Making | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Adult Basic Education, Adult Secondary Education, and English as a Second Language Instructors | Amusement and Recreation Attendants | Baggage Porters and Bellhops | Concierges | Curators | Entertainment and Recreation Managers, Except Gambling | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | Historians | History Teachers, Postsecondary | Instructional Coordinators | Librarians and Media Collections Specialists | Meeting, Convention, and Event Planners | Park Naturalists | Recreation Workers | Reservation and Transportation Ticket Agents and Travel Clerks | Self-Enrichment Teachers | Teaching Assistants, Special Education | Travel Agents | Travel Guides | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Escort individuals or groups on sightseeing tours or through places of interest, such as industrial establishments, public buildings, and art galleries.</t>
+  </si>
+  <si>
+    <t>Assemble and check the required supplies and equipment prior to departure. | Collect fees and tickets from group members. | Conduct educational activities for school children. | Describe tour points of interest to group members, and respond to questions. | Distribute brochures, show audiovisual presentations, and explain establishment processes and operations at tour sites. | Drive motor vehicles to transport visitors to establishments and tour site locations. | Escort individuals or groups on cruises, sightseeing tours, or through places of interest, such as industrial establishments, public buildings, or art galleries. | Greet and register visitors, and issue any required identification badges or safety devices. | Monitor visitors' activities to ensure compliance with establishment or tour regulations and safety practices. | Perform clerical duties, such as filing, typing, operating switchboards, or routing mail and messages. | Provide directions and other pertinent information to visitors. | Provide for physical safety of groups, performing such activities as providing first aid or directing emergency evacuations. | Provide information about wildlife varieties and habitats, as well as any relevant regulations, such as those pertaining to hunting and fishing. | Research various topics, including site history, environmental conditions, and clients' skills and abilities to plan appropriate expeditions, instruction, and commentary. | Select travel routes and sites to be visited based on knowledge of specific areas. | Solicit tour patronage and sell souvenirs. | Speak foreign languages to communicate with foreign visitors. | Teach skills, such as proper climbing methods, and demonstrate and advise on the use of equipment. | Train other guides and volunteers.</t>
+  </si>
+  <si>
+    <t>39-7012.00</t>
+  </si>
+  <si>
+    <t>Travel Guides</t>
+  </si>
+  <si>
+    <t>Cruise Counselor | Guide | Naturalist Guide | Tour Coordinator | Tour Escort | Tour Manager | Tour Operations Specialist | Tour Operator | Travel Consultant | Whitewater Rafting Guide</t>
+  </si>
+  <si>
+    <t>Customer information databases | Data visualization software | Facebook | Financial accounting software | Global positioning system GPS software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Structured query language SQL | Tableau | Travel Agent CMS | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Writing | Critical Thinking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Sales and Marketing | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Written Comprehension | Problem Sensitivity | Near Vision | Deductive Reasoning | Information Ordering | Category Flexibility | Inductive Reasoning | Written Expression | Far Vision | Time Sharing | Selective Attention | Originality</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Determine Tasks, Priorities and Goals | Contact With Others | Freedom to Make Decisions | E-Mail | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Work Outcomes and Results of Other Workers | Health and Safety of Other Workers | Written Letters and Memos | Indoors, Environmentally Controlled | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Baggage Porters and Bellhops | Bus Drivers, Transit and Intercity | Concierges | Counter and Rental Clerks | Customer Service Representatives | Entertainment and Recreation Managers, Except Gambling | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | Flight Attendants | Freight Forwarders | Lodging Managers | Meeting, Convention, and Event Planners | Motorboat Operators | Park Naturalists | Passenger Attendants | Recreation Workers | Reservation and Transportation Ticket Agents and Travel Clerks | Tour Guides and Escorts | Travel Agents | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Plan, organize, and conduct long-distance travel, tours, and expeditions for individuals and groups.</t>
+  </si>
+  <si>
+    <t>Administer first aid to injured group participants. | Arrange for tour or expedition details such as accommodations, transportation, equipment, and the availability of medical personnel. | Attend to special needs of tour participants. | Evaluate services received on the tour, and report findings to tour organizers. | Explain hunting and fishing laws to groups to ensure compliance. | Give advice on sightseeing and shopping. | Instruct novices in climbing techniques, mountaineering, and wilderness survival, and demonstrate use of hunting, fishing, and climbing equipment. | Lead individuals or groups to tour site locations and describe points of interest. | Pay bills and record checks issued. | Pilot airplanes or drive land and water vehicles to transport tourists to activity or tour sites. | Plan tour itineraries, applying knowledge of travel routes and destination sites. | Provide tourists with assistance in obtaining permits and documents such as visas, passports, and health certificates, and in converting currency. | Resolve any problems with itineraries, service, or accommodations. | Sell or rent equipment, clothing, and supplies related to expeditions. | Sell travel packages. | Set up camps, and prepare meals for tour group members. | Verify amounts and quality of equipment prior to expeditions or tours.</t>
+  </si>
+  <si>
+    <t>39-9011.00</t>
+  </si>
+  <si>
+    <t>Childcare Workers</t>
+  </si>
+  <si>
+    <t>Caregiver | Child Care Worker | Child Caregiver | Childcare Provider | Childcare Worker | Daycare Teacher | Daycare Worker | Infant Teacher | Toddler Teacher</t>
+  </si>
+  <si>
+    <t>Educational software | Google Classroom | Microsoft Office software | Microsoft Word | Nearpod | Scheduling software | Schoology | Seesaw | Tadpoles | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking | Learning Strategies | Active Learning | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Education and Training | Public Safety and Security | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Speech Recognition | Far Vision | Deductive Reasoning | Written Comprehension | Near Vision | Time Sharing | Selective Attention | Category Flexibility | Information Ordering | Speech Clarity | Inductive Reasoning | Fluency of Ideas | Written Expression</t>
+  </si>
+  <si>
+    <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Physical Proximity | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Health and Safety of Other Workers | Spend Time Standing | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Education Administrators, Kindergarten through Secondary | Education and Childcare Administrators, Preschool and Daycare | First-Line Supervisors of Personal Service Workers | Health Education Specialists | Home Health Aides | Kindergarten Teachers, Except Special Education | Medical and Health Services Managers | Nannies | Nursing Assistants | Personal Care Aides | Preschool Teachers, Except Special Education | Social and Community Service Managers | Special Education Teachers, Elementary School | Special Education Teachers, Kindergarten | Special Education Teachers, Middle School | Special Education Teachers, Preschool | Special Education Teachers, Secondary School | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education</t>
+  </si>
+  <si>
+    <t>Attend to children at schools, businesses, private households, and childcare institutions. Perform a variety of tasks, such as dressing, feeding, bathing, and overseeing play.</t>
+  </si>
+  <si>
+    <t>Accompany children to and from school, on outings, and to medical appointments. | Assist in preparing food and serving meals and refreshments to children. | Care for children in institutional setting, such as group homes, nursery schools, private businesses, or schools for people with disabilities. | Communicate with children's parents or guardians about daily activities, behaviors, and related issues. | Create developmentally appropriate lesson plans. | Discipline children and recommend or initiate other measures to control behavior, such as caring for own clothing and picking up toys and books. | Dress children and change diapers. | Help children with homework and school work. | Identify signs of emotional or developmental problems in children and bring them to parents' or guardians' attention. | Instruct children in health and personal habits, such as eating, resting, and toilet habits. | Keep records on individual children, including daily observations and information about activities, meals served, and medications administered. | Maintain a safe play environment. | Observe and monitor children's play activities. | Organize and participate in recreational activities and outings, such as games and field trips. | Organize and store toys and materials to ensure order in activity areas. | Perform general administrative tasks, such as taking attendance, editing internal paperwork, and making phone calls. | Perform general personnel functions, such as supervision, training, and scheduling. | Perform housekeeping duties, such as laundry, cleaning, dish washing, and changing of linens. | Provide care for children with physical, developmental, or mental health disabilities. | Read to children and teach them simple painting, drawing, handicrafts, and songs. | Regulate children's rest periods. | Sanitize toys and play equipment. | Sterilize bottles and prepare formulas. | Support children's emotional and social development, encouraging understanding of others and positive self-concepts.</t>
+  </si>
+  <si>
+    <t>39-9011.01</t>
+  </si>
+  <si>
+    <t>Nannies</t>
+  </si>
+  <si>
+    <t>Family Assistant | Family Manager | Governess | House Manager | Household Manager | Nanny | Special Needs Nanny | Travel Nanny</t>
+  </si>
+  <si>
+    <t>Educational software | Microsoft Excel | Microsoft Word | Scheduling software | Web browser software</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Psychology | Education and Training | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Speech Recognition | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Near Vision | Selective Attention | Originality | Fluency of Ideas | Written Expression | Trunk Strength | Information Ordering</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Freedom to Make Decisions | Contact With Others | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Outdoors, Exposed to All Weather Conditions</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Childcare Workers | Education and Childcare Administrators, Preschool and Daycare | First-Line Supervisors of Personal Service Workers | Healthcare Social Workers | Home Health Aides | Kindergarten Teachers, Except Special Education | Licensed Practical and Licensed Vocational Nurses | Nurse Midwives | Nursing Assistants | Occupational Therapists | Occupational Therapy Assistants | Personal Care Aides | Preschool Teachers, Except Special Education | Psychiatric Aides | Registered Nurses | Residential Advisors | Social and Human Service Assistants | Special Education Teachers, Preschool | Teaching Assistants, Special Education</t>
+  </si>
+  <si>
+    <t>Care for children in private households and provide support and expertise to parents in satisfying children's physical, emotional, intellectual, and social needs. Duties may include meal planning and preparation, laundry and clothing care, organization of play activities and outings, discipline, intellectual stimulation, language activities, and transportation.</t>
+  </si>
+  <si>
+    <t>Assign appropriate chores and praise targeted behaviors to encourage development of self-control, self-confidence, and responsibility. | Help develop or monitor family schedule. | Help prepare and serve nutritionally balanced meals and snacks for children. | Instruct and assist children in the development of health and personal habits, such as eating, resting, and toilet behavior. | Instruct children in safe behavior, such as seeking adult assistance when crossing the street and avoiding contact with unsafe objects. | Keep records of play, meal schedules, and bill payment. | Meet regularly with parents to discuss children's activities and development. | Model appropriate social behaviors and encourage concern for others to cultivate development of interpersonal relationships and communication skills. | Observe children's behavior for irregularities, take temperature, transport children to doctor, or administer medications, as directed, to maintain children's health. | Organize and conduct age-appropriate recreational activities, such as games, arts and crafts, sports, walks, and play dates. | Perform first aid or cardiopulmonary resuscitation (CPR) when required. | Perform housekeeping and cleaning duties related to children's care. | Regulate children's rest periods and nap schedules. | Remove hazards and develop appropriate boundaries and rules to create a safe environment for children. | Shop for groceries, clothing, and other items needed for children's care. | Supervise and assist with homework. | Teach and perform age-appropriate activities, such as lap play, reading, and arts and crafts, to encourage intellectual development of children. | Transport children to schools, social outings, and medical appointments. | Work with parents to develop and implement discipline programs to promote desirable child behavior.</t>
+  </si>
+  <si>
+    <t>39-9031.00</t>
+  </si>
+  <si>
+    <t>Exercise Trainers and Group Fitness Instructors</t>
+  </si>
+  <si>
+    <t>Aerobics Instructor | Fitness Instructor | Fitness Specialist | Fitness Trainer | Group Exercise Instructor | Group Fitness Instructor | Personal Trainer | Private Trainer | Strength and Conditioning Coach | Yoga Instructor</t>
+  </si>
+  <si>
+    <t>Appointment scheduling software | BioEx Systems Exercise Expert | BioEx Systems Fitness Maker | BioEx Systems Nutrition Maker Plus | Blink | DaySmart Software Appointment-Plus | DietMaster Systems DietMaster | EZFacility Trainer Management System | Email software | ICTraining | Intuit QuickBooks | MYOB BusinessEssentials | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Online River Software Personal Trainer Pro | Sage 50 Accounting | Sage Simply Accounting | Visual Health Information The Trainer's Exercise Toolbox | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Learning Strategies | Monitoring | Active Learning | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Education and Training | English Language | Psychology</t>
+  </si>
+  <si>
+    <t>Stamina | Extent Flexibility | Gross Body Coordination | Oral Expression | Trunk Strength | Speech Clarity | Dynamic Strength | Static Strength | Fluency of Ideas | Written Comprehension | Oral Comprehension | Explosive Strength | Multilimb Coordination | Manual Dexterity | Selective Attention | Category Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Originality | Speech Recognition | Far Vision | Near Vision | Gross Body Equilibrium | Dynamic Flexibility</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Freedom to Make Decisions | Spend Time Standing | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Physical Proximity | E-Mail | Spend Time Bending or Twisting Your Body | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Public Speaking | Telephone Conversations | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Making Repetitive Motions | Level of Competition | Health and Safety of Other Workers | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Adapted Physical Education Specialists | Animal Trainers | Athletic Trainers | Coaches and Scouts | Dietitians and Nutritionists | Exercise Physiologists | Fitness and Wellness Coordinators | Health Education Specialists | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Recreation Workers | Recreation and Fitness Studies Teachers, Postsecondary | Recreational Therapists | Self-Enrichment Teachers | Training and Development Managers | Training and Development Specialists</t>
+  </si>
+  <si>
+    <t>Instruct or coach groups or individuals in exercise activities for the primary purpose of personal fitness. Demonstrate techniques and form, observe participants, and explain to them corrective measures necessary to improve their skills. Develop and implement individualized approaches to exercise.</t>
+  </si>
+  <si>
+    <t>Administer emergency first aid, wrap injuries, treat minor chronic disabilities, or refer injured persons to physicians. | Advise clients about proper clothing and shoes. | Advise participants in use of heat or ultraviolet treatments and hot baths. | Conduct therapeutic, recreational, or athletic activities. | Evaluate individuals' abilities, needs, and physical conditions, and develop suitable training programs to meet any special requirements. | Explain and enforce safety rules and regulations governing sports, recreational activities, and the use of exercise equipment. | Instruct participants in maintaining exertion levels to maximize benefits from exercise routines. | Maintain equipment inventories, and select, store, or issue equipment as needed. | Maintain fitness equipment. | Monitor participants' progress and adapt programs as needed. | Observe participants and inform them of corrective measures necessary for skill improvement. | Offer alternatives during classes to accommodate different levels of fitness. | Organize and conduct competitions and tournaments. | Plan physical education programs to promote development of participants' physical attributes and social skills. | Plan routines, choose appropriate music, and choose different movements for each set of muscles, depending on participants' capabilities and limitations. | Promote health clubs through membership sales, and record member information. | Provide students with information and resources regarding nutrition, weight control, and lifestyle issues. | Teach and demonstrate use of gymnastic and training equipment, such as trampolines and weights. | Teach individual and team sports to participants through instruction and demonstration, using knowledge of sports techniques and of participants' physical capabilities. | Teach proper breathing techniques used during physical exertion.</t>
+  </si>
+  <si>
+    <t>39-9032.00</t>
+  </si>
+  <si>
+    <t>Recreation Workers</t>
+  </si>
+  <si>
+    <t>Activities Assistant | Activities Director | Activity Aide | Activity Assistant | Activity Coordinator | Activity Director | Recreation Assistant | Recreation Coordinator | Recreation Supervisor</t>
+  </si>
+  <si>
+    <t>Appletree | Corel WordPerfect Office Suite | Database software | GroupMe | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | Recordkeeping software | Scheduling software | YouTube</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Critical Thinking | Learning Strategies | Reading Comprehension | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>English Language | Public Safety and Security | Customer and Personal Service | Education and Training | Law and Government | Psychology | Administrative | Computers and Electronics | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Near Vision | Speech Recognition | Problem Sensitivity | Written Comprehension | Deductive Reasoning | Category Flexibility | Information Ordering | Originality | Fluency of Ideas | Written Expression | Far Vision | Time Sharing | Selective Attention | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Frequency of Decision Making | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Deal With External Customers or the Public in General | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Community Health Workers | Directors, Religious Activities and Education | Education Administrators, Kindergarten through Secondary | Education and Childcare Administrators, Preschool and Daycare | Educational, Guidance, and Career Counselors and Advisors | Entertainment and Recreation Managers, Except Gambling | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Personal Service Workers | Fitness and Wellness Coordinators | Health Education Specialists | Instructional Coordinators | Recreation and Fitness Studies Teachers, Postsecondary | Recreational Therapists | Rehabilitation Counselors | Residential Advisors | Social and Community Service Managers | Social and Human Service Assistants | Training and Development Managers | Training and Development Specialists</t>
+  </si>
+  <si>
+    <t>Conduct recreation activities with groups in public, private, or volunteer agencies or recreation facilities. Organize and promote activities, such as arts and crafts, sports, games, music, dramatics, social recreation, camping, and hobbies, taking into account the needs and interests of individual members.</t>
+  </si>
+  <si>
+    <t>Administer first aid according to prescribed procedures and notify emergency medical personnel when necessary. | Assess the needs and interests of individuals and groups and plan activities accordingly, given the available equipment or facilities. | Complete and maintain time and attendance forms and inventory lists. | Conduct individual in-room visits with residents. | Confer with management to discuss and resolve participant complaints. | Develop treatment goals for individuals based on their assessments. | Direct special activities or events, such as aquatics, gymnastics, or performing arts. | Document individuals' progress toward meeting their treatment goals. | Encourage participants to develop their own activities and leadership skills through group discussions. | Enforce rules and regulations of recreational facilities to maintain discipline and ensure safety. | Evaluate recreation areas, facilities, and services to determine if they are producing desired results. | Evaluate staff performance, recording evaluations on appropriate forms. | Explain principles, techniques, and safety procedures to participants in recreational activities and demonstrate use of materials and equipment. | Greet new arrivals to activities, introducing them to other participants, explaining facility rules, and encouraging participation. | Manage the daily operations of recreational facilities. | Meet and collaborate with agency personnel, community organizations, and other professional personnel to plan balanced recreational programs for participants. | Meet with staff to discuss rules, regulations, and work-related problems. | Organize, lead, and promote interest in recreational activities, such as arts, crafts, sports, games, camping, and hobbies. | Oversee the purchase, planning, design, construction, and upkeep of recreation facilities and areas. | Provide for entertainment and set up related decorations and equipment. | Schedule maintenance and use of facilities. | Serve as liaison between park or recreation administrators and activity instructors. | Supervise and coordinate the work activities of personnel, such as training staff members and assigning work duties. | Take residents on community outings.</t>
+  </si>
+  <si>
+    <t>39-9041.00</t>
+  </si>
+  <si>
+    <t>Residential Advisors</t>
+  </si>
+  <si>
+    <t>Hall Coordinator | Residence Director | Residence Hall Director | Residence Life Coordinator | Residence Life Director | Resident Advisor | Resident Assistant | Resident Director | Residential Coordinator | Residential Life Director</t>
+  </si>
+  <si>
+    <t>Budgeting software | Email software | Google Docs | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Survey software | Web browser software | Website development software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Critical Thinking | Reading Comprehension | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | Public Safety and Security | Education and Training | English Language | Sociology and Anthropology | Administrative | Personnel and Human Resources | Therapy and Counseling | Psychology | Communications and Media | Computers and Electronics | Law and Government</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Speech Clarity | Speech Recognition | Written Comprehension | Deductive Reasoning | Inductive Reasoning | Near Vision | Written Expression | Far Vision | Selective Attention | Information Ordering</t>
+  </si>
+  <si>
+    <t>E-Mail | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Telephone Conversations | Health and Safety of Other Workers | Conflict Situations | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Indoors, Environmentally Controlled | Work Outcomes and Results of Other Workers | Impact of Decisions on Co-workers or Company Results | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Directors, Religious Activities and Education | Education Administrators, Kindergarten through Secondary | Education Administrators, Postsecondary | Education and Childcare Administrators, Preschool and Daycare | Educational, Guidance, and Career Counselors and Advisors | Eligibility Interviewers, Government Programs | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Personal Service Workers | Health Education Specialists | Home Health Aides | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Patient Representatives | Personal Care Aides | Recreation Workers | Rehabilitation Counselors | Social and Community Service Managers | Social and Human Service Assistants</t>
+  </si>
+  <si>
+    <t>Coordinate activities in resident facilities in secondary school and college dormitories, group homes, or similar establishments. Order supplies and determine need for maintenance, repairs, and furnishings. May maintain household records and assign rooms. May assist residents with problem solving or refer them to counseling resources.</t>
+  </si>
+  <si>
+    <t>Accompany and supervise students during meals. | Administer, coordinate, or recommend disciplinary and corrective actions. | Answer telephones, and route calls or deliver messages. | Assign rooms to students. | Chaperone group-sponsored trips and social functions. | Collaborate with counselors to develop counseling programs that address the needs of individual students. | Communicate with other staff to resolve problems with individual students. | Compile information such as residents' daily activities and the quantities of supplies used to prepare required reports. | Confer with medical personnel to better understand the backgrounds and needs of individual residents. | Counsel students in the handling of issues such as family, financial, and educational problems. | Determine the need for facility maintenance and repair, and notify appropriate personnel. | Develop and coordinate educational programs for residents. | Develop program plans for individuals or assist in plan development. | Direct and participate in on- and off-campus recreational activities for residents of institutions, boarding schools, fraternities or sororities, children's homes, or similar establishments. | Enforce rules and regulations to ensure the smooth and orderly operation of dormitory programs. | Hold regular meetings with each assigned unit. | Inventory, pack, and remove items left behind by former residents. | Make regular rounds to ensure that residents and areas are safe and secure. | Mediate interpersonal problems between residents. | Observe students to detect and report unusual behavior. | Order supplies for facilities. | Oversee departmental budget. | Process contract cancellations for students who are unable to follow residence hall policies and procedures. | Provide emergency first aid and summon medical assistance when necessary. | Provide requested information on students' progress and the development of case plans. | Provide transportation or escort for expeditions, such as shopping trips or visits to doctors or dentists. | Sort and distribute mail. | Supervise students' housekeeping work to ensure that it is done properly. | Supervise the activities of housekeeping personnel. | Supervise, train, and evaluate residence hall staff, including resident assistants, participants in work-study programs, and other student workers.</t>
+  </si>
+  <si>
+    <t>39-9099.00</t>
+  </si>
+  <si>
+    <t>Personal Care and Service Workers, All Other</t>
+  </si>
+  <si>
+    <t>Companion | Home Companion | Personal Assistant | Personal Attendant | Personal Care Worker | Personal Service Worker | Pet Sitter | Sitter | Wellness Attendant | Client Care Attendant</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Email software | Web browser software | Database software | Scheduling software | Microsoft Outlook | Inventory management systems | Microsoft Office software | Computerized maintenance management system CMMS</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Psychology | Education and Training | Public Safety and Security | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Personal Care Aides | Home Health Aides | Childcare Workers | Nannies | Residential Advisors | Recreation Workers | Exercise Trainers and Group Fitness Instructors | Animal Caretakers | Animal Trainers | Concierges | Tour Guides and Escorts | Travel Guides | Barbers | Hairdressers, Hairstylists, and Cosmetologists | Skincare Specialists | Manicurists and Pedicurists | Massage Therapists | Nursing Assistants | Social and Human Service Assistants | First-Line Supervisors of Personal Service Workers</t>
+  </si>
+  <si>
+    <t>All personal care and service workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Provide personal care and service in roles not classified separately. | Assist clients with daily activities, errands, and personal routines. | Accompany clients to appointments, activities, and social events. | Provide companionship, conversation, and supervision to clients. | Prepare meals, perform light housekeeping, and maintain client living areas. | Monitor client wellbeing and report concerns to families or supervisors. | Schedule and coordinate appointments, services, and transportation. | Maintain records of services provided, hours worked, and expenses. | Follow care plans and instructions established by families or agencies. | Respond to emergencies and summon appropriate assistance. | Care for pets, plants, and household items as agreed with clients. | Respect client privacy, dignity, and confidentiality at all times. | Purchase supplies and manage household budgets on behalf of clients. | Communicate regularly with family members and care coordinators.</t>
+  </si>
+  <si>
+    <t>41-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Retail Sales Workers</t>
+  </si>
+  <si>
+    <t>Bakery Manager | Delicatessen Manager | Department Manager | Department Supervisor | Grocery Manager | Key Carrier | Meat Department Manager | Parts Sales Manager | Shift Manager | Store Manager</t>
+  </si>
+  <si>
+    <t>ASI Point of Sale | Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | American Precision Instruments Regit | Apple Final Cut Pro | Apple Safari | Attitude POS itive AccuPOS Retail | Autodesk Revit | Bibase 4POS Retail | CAP Automation SellWise | Comcash ERP | CompuTant CounterPoint | CyberMatrix POS | Data entry software | Datasym SYMFINITE | Delphi Technology | EZ Software Solutions | Exact business software | Facebook | FileMaker Pro | Gift registry software | Google Ads | Google Analytics | Google Docs | Google Drive | Google Meet | Hagel Unitime Systems | Handheld computer device software | Human resource management software HRMS | IBM Cognos Impromptu | IBM Notes | IBM SPSS Statistics | Infocorp Computer Solutions $mart System | Infocorp Softwear/POS | Intuit QuickBooks Point of Sale | Inventory management systems | Kronos Enterprise Workforce Management | Kronos Workforce Timekeeper | LOB RetailPoint | Lathem Time PayClock EZ | LinkedIn | Logisoft Positive Pos System | ManageMore Cellular Manager | Master Merchant Systems Music Store | MicroBiz | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Millennium Software Atrex | Minitab | Mozilla Firefox | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Taleo | Payroll software | Plexis Software Plexis POS | Point of sale POS bookstore software | Point of sale POS parts and services software | Qlik Tech QlikView | Qualitech Solutions Dynamic Scheduling | R | RiscStation POSSum | SAP software | SAS | SBS Keystroke | Sage 50 Accounting | Sage 50 Accounting Software | Salesforce software | Scheduling software | Semicron Systems | SmugMug Flickr | Social media sites | Softpedia ShopInvo | StataCorp Stata | System3 POS software | Tableau | Teradata Database | The General Store | The Retail Solution | Time card software | TimeTrak Systems ClocTrack | TimeTrak Systems SchedTrak | True North Computer Retail Plus | VeriFone PC Charge Pro | Vigilant | Visual Retail Plus | WinMan SureSell | Yardi software | YouTube</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Monitoring | Learning Strategies | Active Learning | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | Sales and Marketing | English Language | Education and Training | Personnel and Human Resources | Mathematics | Computers and Electronics | Economics and Accounting | Administrative</t>
+  </si>
+  <si>
+    <t>Speech Clarity | Oral Comprehension | Oral Expression | Speech Recognition | Problem Sensitivity | Near Vision | Information Ordering | Deductive Reasoning | Originality | Fluency of Ideas | Written Expression | Written Comprehension | Selective Attention | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Frequency of Decision Making | Time Pressure | Determine Tasks, Priorities and Goals | E-Mail | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Repeating Same Tasks | Written Letters and Memos | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Cashiers | Counter and Rental Clerks | Customer Service Representatives | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | General and Operations Managers | Retail Salespersons | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Stockers and Order Fillers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of retail sales workers in an establishment or department. Duties may include management functions, such as purchasing, budgeting, accounting, and personnel work, in addition to supervisory duties.</t>
+  </si>
+  <si>
+    <t>Assign employees to specific duties. | Confer with company officials to develop methods and procedures to increase sales, expand markets, and promote business. | Direct and supervise employees engaged in sales, inventory-taking, reconciling cash receipts, or in performing services for customers. | Enforce safety, health, and security rules. | Establish and implement policies, goals, objectives, and procedures for the department. | Establish credit policies and operating procedures. | Estimate consumer demand and determine the types and amounts of goods to be sold. | Examine merchandise to ensure that it is correctly priced and displayed and that it functions as advertised. | Examine products purchased for resale or received for storage to assess the condition of each product or item. | Formulate pricing policies for merchandise, according to profitability requirements. | Hire, train, and evaluate personnel in sales or marketing establishments, promoting or firing workers when appropriate. | Instruct staff on how to handle difficult and complicated sales. | Inventory stock and reorder when inventory drops to a specified level. | Keep records of purchases, sales, and requisitions. | Monitor sales activities to ensure that customers receive satisfactory service and quality goods. | Perform work activities of subordinates, such as cleaning and organizing shelves and displays and selling merchandise. | Plan and coordinate advertising campaigns and sales promotions and prepare merchandise displays and advertising copy. | Plan and prepare work schedules and keep records of employees' work schedules and time cards. | Plan budgets and authorize payments and merchandise returns. | Provide customer service by greeting and assisting customers and responding to customer inquiries and complaints. | Review inventory and sales records to prepare reports for management and budget departments.</t>
+  </si>
+  <si>
+    <t>41-1012.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Non-Retail Sales Workers</t>
+  </si>
+  <si>
+    <t>Customer Service Department Supervisor | Customer Service Supervisor | Driver Sales Supervisor | Information Center Supervisor | Inside Sales Supervisor | Reservations Supervisor | Sales Department Supervisor | Sales Leader | Sales Supervisor | Sales Team Leader</t>
+  </si>
+  <si>
+    <t>Budgeting software | Cisco Webex | Customer information databases | Delphi Discovery | Delphi Technology | Electronic data interchange EDI software | Financial accounting software | Flow chart software | Fuze cloud communications and collaboration software | Graphics creation software | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | NetSuite ERP | Online meeting software | Oracle Eloqua | QuickBase business management software | SAP software | Salesforce software | Salesforce.com Salesforce CRM | SugarCRM Sugar UX | Web browser software | Work scheduling software | YouTube</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Reading Comprehension | Writing | Critical Thinking | Active Learning | Learning Strategies | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | English Language | Personnel and Human Resources | Economics and Accounting | Sales and Marketing | Mathematics | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Written Comprehension | Deductive Reasoning | Inductive Reasoning | Information Ordering | Near Vision | Category Flexibility | Problem Sensitivity | Fluency of Ideas | Written Expression | Mathematical Reasoning | Number Facility</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Time Pressure | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Work Outcomes and Results of Other Workers | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Written Letters and Memos | Spend Time Sitting | Importance of Repeating Same Tasks | Health and Safety of Other Workers | Level of Competition | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Customer Service Representatives | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Human Resources Specialists | Management Analysts | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of sales workers other than retail sales workers. May perform duties such as budgeting, accounting, and personnel work, in addition to supervisory duties.</t>
+  </si>
+  <si>
+    <t>Analyze details of sales territories to assess their growth potential and to set quotas. | Attend company meetings to exchange product information and coordinate work activities with other departments. | Confer with company officials to develop methods and procedures to increase sales, expand markets, and promote business. | Coordinate sales promotion activities, such as preparing merchandise displays and advertising copy. | Direct and supervise employees engaged in sales, inventory-taking, reconciling cash receipts, or performing specific services. | Examine merchandise to ensure correct pricing and display, and that it functions as advertised. | Examine products purchased for resale or received for storage to determine product condition. | Formulate pricing policies on merchandise according to profitability requirements. | Hire, train, and evaluate personnel. | Inventory stock and reorder when inventories drop to specified levels. | Keep records pertaining to purchases, sales, and requisitions. | Listen to and resolve customer complaints regarding services, products, or personnel. | Monitor sales staff performance to ensure that goals are met. | Plan and prepare work schedules, and assign employees to specific duties. | Prepare rental or lease agreements, specifying charges and payment procedures for use of machinery, tools, or other items. | Prepare sales and inventory reports for management and budget departments. | Provide staff with assistance in performing difficult or complicated duties. | Visit retailers and sales representatives to promote products and gather information.</t>
+  </si>
+  <si>
+    <t>41-2011.00</t>
+  </si>
+  <si>
+    <t>Cashiers</t>
+  </si>
+  <si>
+    <t>Cage Cashier | Cashier | Center Aisle Cashier | Central Aisle Cashier | Checker | Customer Assistant | Sales Associate | Store Attendant | Store Clerk | Toll Collector</t>
+  </si>
+  <si>
+    <t>AFEXDirect | Apple Safari | Bookkeeping software | Database software | Electronic medical record EMR software | Handheld computer device software | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Windows | Mozilla Firefox | ReliaSoft Prism</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Speech Clarity | Written Comprehension | Problem Sensitivity | Speech Recognition | Information Ordering</t>
+  </si>
+  <si>
+    <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Standing | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Counter and Rental Clerks | Customer Service Representatives | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Retail Sales Workers | Gambling Cage Workers | Gambling Change Persons and Booth Cashiers | Hotel, Motel, and Resort Desk Clerks | New Accounts Clerks | Office Clerks, General | Order Clerks | Pharmacy Aides | Postal Service Clerks | Receptionists and Information Clerks | Retail Salespersons | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Telemarketers | Tellers</t>
+  </si>
+  <si>
+    <t>Receive and disburse money in establishments other than financial institutions. May use electronic scanners, cash registers, or related equipment. May process credit or debit card transactions and validate checks.</t>
+  </si>
+  <si>
+    <t>Answer customers' questions, and provide information on procedures or policies. | Answer incoming phone calls. | Assist customers by providing information and resolving their complaints. | Assist with duties in other areas of the store, such as monitoring fitting rooms or bagging and carrying out customers' items. | Bag, box, wrap, or gift-wrap merchandise, and prepare packages for shipment. | Calculate total payments received during a time period, and reconcile this with total sales. | Cash checks for customers. | Compile and maintain non-monetary reports and records. | Compute and record totals of transactions. | Count money in cash drawers at the beginning of shifts to ensure that amounts are correct and that there is adequate change. | Establish or identify prices of goods, services, or admission, and tabulate bills, using calculators, cash registers, or optical price scanners. | Greet customers entering establishments. | Help customers find the location of products. | Issue receipts, refunds, credits, or change due to customers. | Issue trading stamps, and redeem food stamps and coupons. | Keep periodic balance sheets of amounts and numbers of transactions. | Maintain clean and orderly checkout areas, and complete other general cleaning duties, such as mopping floors and emptying trash cans. | Monitor checkout stations to ensure they have adequate cash available and are staffed appropriately. | Offer customers carry-out service at the completion of transactions. | Post charges against guests' or patients' accounts. | Process merchandise returns and exchanges. | Receive payment by cash, check, credit cards, vouchers, or automatic debits. | Request information or assistance, using paging systems. | Sell tickets and other items to customers. | Sort, count, and wrap currency and coins. | Stock shelves, sort and reshelve returned items, and mark prices on items and shelves. | Supervise others and provide on-the-job training. | Weigh items sold by weight to determine prices.</t>
+  </si>
+  <si>
+    <t>41-2012.00</t>
+  </si>
+  <si>
+    <t>Gambling Change Persons and Booth Cashiers</t>
+  </si>
+  <si>
+    <t>Booth Cashier | Cage Cashier | Cashier | Casino Banker | Casino Cashier | Change Person | Slot Attendant | Slot Floor Person | Slot Technician | Vault Cashier</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Near Vision | Oral Expression | Problem Sensitivity | Information Ordering | Speech Recognition | Number Facility | Mathematical Reasoning | Speech Clarity | Written Comprehension | Finger Dexterity | Perceptual Speed | Inductive Reasoning | Deductive Reasoning | Arm-Hand Steadiness</t>
+  </si>
+  <si>
+    <t>Contact With Others | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks | Spend Time Standing | Deal With External Customers or the Public in General | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Telephone Conversations | Physical Proximity | Work With or Contribute to a Work Group or Team | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Cashiers | Coin, Vending, and Amusement Machine Servicers and Repairers | Counter and Rental Clerks | Credit Authorizers, Checkers, and Clerks | Data Entry Keyers | First-Line Supervisors of Gambling Services Workers | Gambling Cage Workers | Gambling Dealers | Gambling Managers | Gambling Surveillance Officers and Gambling Investigators | Gambling and Sports Book Writers and Runners | Hotel, Motel, and Resort Desk Clerks | Mail Clerks and Mail Machine Operators, Except Postal Service | New Accounts Clerks | Office Clerks, General | Receptionists and Information Clerks | Stockers and Order Fillers | Tellers</t>
+  </si>
+  <si>
+    <t>Exchange coins, tokens, and chips for patrons' money. May issue payoffs and obtain customer's signature on receipt. May operate a booth in the slot machine area and furnish change persons with money bank at the start of the shift, or count and audit money in drawers.</t>
+  </si>
+  <si>
+    <t>Accept credit applications and verify credit references to provide check-cashing authorization or to establish house credit accounts. | Calculate the value of chips won or lost by players. | Check identifications to verify age of players. | Clean casino areas. | Count money and audit money drawers. | Exchange money, credit, tickets, or casino chips and make change for customers. | Furnish change persons with a money bank at the start of each shift. | Keep accurate records of monetary exchanges, authorization forms, and transaction reconciliations. | Listen for jackpot alarm bells and issue payoffs to winners. | Maintain cage security according to rules. | Obtain customers' signatures on receipts when winnings exceed the amount held in a slot machine. | Reconcile daily summaries of transactions to balance books. | Sell gambling chips, tokens, or tickets to patrons, or to other workers for resale to patrons.</t>
+  </si>
+  <si>
+    <t>41-2021.00</t>
+  </si>
+  <si>
+    <t>Counter and Rental Clerks</t>
+  </si>
+  <si>
+    <t>Counter Clerk | Counter Service Representative | Leasing Consultant | Rental Agent | Rental Assistant | Rental Associate | Rental Clerk | Rental Counter Clerk | Rental Sales Representative | Video Clerk</t>
+  </si>
+  <si>
+    <t>Database software | Inventory management systems | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Database</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Sales and Marketing | Administration and Management | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Near Vision | Written Comprehension | Information Ordering | Problem Sensitivity | Selective Attention | Written Expression</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Frequency of Decision Making | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Being Exact or Accurate | E-Mail | Freedom to Make Decisions | Conflict Situations | Physical Proximity | Importance of Repeating Same Tasks | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Cashiers | Concierges | Customer Service Representatives | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Retail Sales Workers | Hotel, Motel, and Resort Desk Clerks | Order Clerks | Parts Salespersons | Postal Service Clerks | Procurement Clerks | Receptionists and Information Clerks | Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Receive orders, generally in person, for repairs, rentals, and services. May describe available options, compute cost, and accept payment.</t>
+  </si>
+  <si>
+    <t>Advise customers on use and care of merchandise. | Allocate equipment to participants in sporting events or recreational activities. | Answer telephones to provide information and receive orders. | Compute charges for merchandise or services and receive payments. | Explain rental fees, policies, and procedures. | Greet customers and discuss the type, quality, and quantity of merchandise sought for rental. | Inspect and adjust rental items to meet needs of customer. | Keep records of transactions and of the number of customers entering an establishment. | Prepare merchandise for display or for purchase or rental. | Prepare rental forms, obtaining customer signature and other information, such as required licenses. | Provide information about rental items, such as availability, operation, or description. | Receive orders for services, such as rentals, repairs, dry cleaning, and storage. | Receive, examine, and tag articles to be altered, cleaned, stored, or repaired. | Recommend and provide advice on a wide variety of products and services. | Rent items, arrange for provision of services to customers, and accept returns. | Reserve items for requested times and keep records of items rented.</t>
+  </si>
+  <si>
+    <t>41-2022.00</t>
+  </si>
+  <si>
+    <t>Parts Salespersons</t>
+  </si>
+  <si>
+    <t>Parts Advisor | Parts Consultant | Parts Counter Salesperson | Parts Counterman | Parts Counterperson | Parts Person | Parts Salesman | Parts Salesperson | Parts Specialist | Wholesale Parts Salesperson</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Customer information databases | Inventory control system software | Inventory management systems | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software | SmugMug Flickr | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | Administration and Management | Administrative | Computers and Electronics | English Language | Economics and Accounting | Production and Processing | Personnel and Human Resources | Mathematics | Mechanical</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Speech Recognition | Written Comprehension | Speech Clarity | Information Ordering | Written Expression | Problem Sensitivity | Inductive Reasoning | Category Flexibility | Deductive Reasoning | Finger Dexterity | Selective Attention | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>Contact With Others | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Telephone Conversations | Freedom to Make Decisions | E-Mail | Indoors, Not Environmentally Controlled | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Time Pressure | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Dealing With Unpleasant, Angry, or Discourteous People | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Exposed to Contaminants | Spend Time Standing | Exposed to Very Hot or Cold Temperatures | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Automotive and Watercraft Service Attendants | Counter and Rental Clerks | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Electric Motor, Power Tool, and Related Repairers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Home Appliance Repairers | Laborers and Freight, Stock, and Material Movers, Hand | Motorboat Mechanics and Service Technicians | Order Clerks | Outdoor Power Equipment and Other Small Engine Mechanics | Production, Planning, and Expediting Clerks | Retail Salespersons | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Team Assemblers</t>
+  </si>
+  <si>
+    <t>Sell spare and replacement parts and equipment in repair shop or parts store.</t>
+  </si>
+  <si>
+    <t>Advise customers on substitution or modification of parts when identical replacements are not available. | Assist customers, such as responding to customer complaints and updating them about back-ordered parts. | Demonstrate equipment to customers, and explain functioning of equipment. | Determine replacement parts required, according to inspections of old parts, customer requests, or customers' descriptions of malfunctions. | Discuss use and features of various parts, based on knowledge of machines or equipment. | Examine returned parts for defects, and exchange defective parts or refund money. | Fill customer orders from stock, and place orders when requested items are out of stock. | Locate and label parts, and maintain inventory of stock. | Maintain and clean work and inventory areas. | Manage shipments by researching shipping methods or costs and tracking packages. | Mark and store parts in stockrooms, according to prearranged systems. | Measure parts, using precision measuring instruments, to determine whether similar parts may be machined to required sizes. | Pick up and deliver parts. | Place new merchandise on display. | Prepare sales slips or sales contracts. | Read catalogs, microfiche viewers, or computer displays to determine replacement part stock numbers and prices. | Receive and fill telephone orders for parts. | Receive payment or obtain credit authorization. | Repair parts or equipment.</t>
+  </si>
+  <si>
+    <t>41-2031.00</t>
+  </si>
+  <si>
+    <t>Retail Salespersons</t>
+  </si>
+  <si>
+    <t>Car Salesman | Customer Assistant | Retail Salesperson | Sales Associate | Sales Clerk | Sales Consultant | Sales Person | Sales Representative | Salesman</t>
+  </si>
+  <si>
+    <t>ASI Point of Sale | Adobe Acrobat | Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Advanced Retail Management Systems Retail Pro | American Precision Instruments Regit | Apple Safari | Apple macOS | Attitude POS itive AccuPOS Retail | Autodesk AutoCAD | Bibase 4POS Retail | Blink | CAP Automation SellWise | Comcash ERP | CompuTant CounterPoint | CyberMatrix | Data entry software | Database software | Datasym SYMFINITE | EZ Software Solutions | Eclipse IDE | Exact business software | Facebook | FileMaker Pro | Gift registry software | Google Docs | Google Drive | Google Meet | GroupMe | Handheld computer device software | IBM Notes | Infocorp Computer Solutions $mart System | Infocorp Softwear/POS | Intuit QuickBooks | Inventory management systems | LOB RetailPoint | LinkedIn | Logisoft Positive Pos System | ManageMore Cellular Manager | Master Merchant Systems Music Store | MicroBiz | Microsoft Access | Microsoft Dynamics | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Millennium Software Atrex | Mozilla Firefox | Oracle PeopleSoft | Plexis Software Plexis POS | Point of sale POS bookstore software | Point of sale POS parts and services software | RiscStation POSSum | SAP software | SBS Keystroke | Sage 50 Accounting | Sage 50 Accounting Software | Salesforce software | Semicron Systems | SmugMug Flickr | Social media sites | Softpedia ShopInvo | System3 POS software | The General Store | The Retail Solution | TokenWorks Magnetic Card Reader | True North Computer Retail Plus | VeriFone PC Charge Pro | Vigilant | Visual Retail Plus | WinMan SureSell | YouTube | iQmetrix RQ4 Retail Management System</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Monitoring | Active Learning | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Sales and Marketing | Customer and Personal Service | English Language | Administration and Management | Mathematics | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Clarity | Speech Recognition | Problem Sensitivity | Near Vision | Information Ordering | Written Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | E-Mail | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Walking or Running | Physical Proximity | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Buyers and Purchasing Agents, Farm Products | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Retail Sales Workers | Merchandise Displayers and Window Trimmers | Order Clerks | Parts Salespersons | Procurement Clerks | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Sell merchandise, such as furniture, motor vehicles, appliances, or apparel to consumers.</t>
+  </si>
+  <si>
+    <t>Answer questions regarding the store and its merchandise. | Bag or package purchases and wrap gifts. | Clean shelves, counters, and tables. | Compute sales prices, total purchases, and receive and process cash or credit payment. | Demonstrate use or operation of merchandise. | Describe merchandise and explain use, operation, and care of merchandise to customers. | Estimate and quote trade-in allowances. | Estimate cost of repair or alteration of merchandise. | Estimate quantity and cost of merchandise required, such as paint or floor covering. | Exchange merchandise for customers and accept returns. | Greet customers and ascertain what each customer wants or needs. | Help customers try on or fit merchandise. | Inventory stock and requisition new stock. | Maintain knowledge of current sales and promotions, policies regarding payment and exchanges, and security practices. | Maintain records related to sales. | Open and close cash registers, performing tasks such as counting money, separating charge slips, coupons, and vouchers, balancing cash drawers, and making deposits. | Place special orders or call other stores to find desired items. | Prepare merchandise for purchase or rental. | Prepare sales slips or sales contracts. | Recommend, select, and help locate or obtain merchandise based on customer needs and desires. | Rent merchandise to customers. | Sell or arrange for delivery, insurance, financing, or service contracts for merchandise. | Ticket, arrange, and display merchandise to promote sales. | Watch for and recognize security risks and thefts and know how to prevent or handle these situations.</t>
+  </si>
+  <si>
+    <t>41-3011.00</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents</t>
+  </si>
+  <si>
+    <t>Advertising Account Representative | Advertising Consultant | Advertising Representative | Advertising Sales Representative (Ad Sales Representative) | Sales Representative</t>
+  </si>
+  <si>
+    <t>Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Canva | Contact management software | Email software | Facebook | FileMaker Pro | Google Ads | Google Analytics | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | QuarkXPress | Salesforce software | Web browser software | WordPress</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Sales and Marketing | Customer and Personal Service | English Language | Communications and Media | Mathematics | Administrative | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Speech Clarity | Oral Expression | Oral Comprehension | Speech Recognition | Written Comprehension | Written Expression | Near Vision | Originality | Fluency of Ideas | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Selective Attention | Category Flexibility | Information Ordering</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Deal With External Customers or the Public in General | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Level of Competition | Time Pressure | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Written Letters and Memos | In an Enclosed Vehicle or Operate Enclosed Equipment | Importance of Being Exact or Accurate | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Advertising and Promotions Managers | Agents and Business Managers of Artists, Performers, and Athletes | Counter and Rental Clerks | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Market Research Analysts and Marketing Specialists | Marketing Managers | Merchandise Displayers and Window Trimmers | Online Merchants | Public Relations Managers | Public Relations Specialists | Real Estate Sales Agents | Retail Salespersons | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Search Marketing Strategists | Telemarketers | Wholesale and Retail Buyers, Except Farm Products | Writers and Authors</t>
+  </si>
+  <si>
+    <t>Sell or solicit advertising space, time, or media in publications, signage, TV, radio, or Internet establishments or public spaces.</t>
+  </si>
+  <si>
+    <t>Arrange for commercial taping sessions, and accompany clients to sessions. | Attend sales meetings, industry trade shows, and training seminars to gather information, promote products, expand network of contacts, and increase knowledge. | Consult with company officials, sales departments, and advertising agencies to develop promotional plans. | Deliver advertising or illustration proofs to customers for approval. | Determine advertising medium to be used, and prepare sample advertisements within the selected medium for presentation to customers. | Draw up contracts for advertising work, and collect payments due. | Explain to customers how specific types of advertising will help promote their products or services in the most effective way possible. | Gather all relevant material for bid processes, and coordinate bidding and contract approval. | Identify new advertising markets, and propose products to serve them. | Inform customers of available options for advertisement artwork, and provide samples. | Locate and contact potential clients to offer advertising services. | Maintain assigned account bases while developing new accounts. | Obtain and study information about clients' products, needs, problems, advertising history, and business practices to offer effective sales presentations and appropriate product assistance. | Prepare and deliver sales presentations to new and existing customers to sell new advertising programs and to protect and increase existing advertising. | Prepare promotional plans, sales literature, media kits, and sales contracts, using computer. | Process all correspondence and paperwork related to accounts. | Provide clients with estimates of the costs of advertising products or services. | Recommend appropriate sizes and formats for advertising, depending on medium used. | Write copy as part of layout. | Write sales outlines for use by staff.</t>
+  </si>
+  <si>
+    <t>41-3021.00</t>
+  </si>
+  <si>
+    <t>Insurance Sales Agents</t>
+  </si>
+  <si>
+    <t>Insurance Agent | Insurance Broker | Insurance Sales Agent | Sales Agent | Sales Associate | Sales Representative | Underwriting Sales Representative</t>
+  </si>
+  <si>
+    <t>AMS Services AMS 360 | AMS Services AMS Sagitta | Adobe After Effects | Advantage Information Systems The Agency Advantage | Agency Master | Agency Software AgencyPro | Agency management software | Allied Financial Software Act4Advisors | Allstar Software Systems Kofax | Apple Final Cut Pro | Applied Systems The Agency Manager | Applied Systems Vision | Benefits Technology Group SalesLogix | CPU Tracker Software CPU Tracker | CoVirt VirtGate | Cygnus Software IncomeMax | DORIS FILESERVERonline | E-Z Data SmartOffice | FINEOS Insure | Facebook | Fiserv FSC Manager | G2X Agility:Insurance | GBS Agency Expert | GroupMe | Healthcare common procedure coding system HCPCS | Hoffman Computer Systems Amsoft | InStar Orion | Infospectrum Quick Insure | Insurance Systems WebWriter BackOffice | Insurance Technologies Corporation InsurancePro | Insurance Technologies ForeSight Enterprise | Insurance Technology Consultants WOW | Insurance analysis software | Insurance rating software | LIDP Consulting Services The Administrator | LinkedIn | LogMeIn GoToMeeting | MI-Assistant MI Management System | Medical procedure coding software | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | NaviSys Front Office | North American Software Associates Eclipse | Online Database Solutions Agent Intelligence | QuickQuote QuickFile Agency Management System | Results International Systems Artius Suite | Scheduling software | Skywire Software Policyware | Special Agent | Tangle S Creations Your Insurance Office | Terrace Consulting AgencyInsight | Tritech Financial Systems General Insurance Management System GIMS | Underwriting software | United Systems and Software Individual Life and Health Administration System | Vulcan Solutions Vulcan Insurance | Web browser software | YouTube | Zoom | irs-aims MARS</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Speaking | Critical Thinking | Writing | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | English Language | Mathematics | Law and Government | Transportation | Administration and Management | Education and Training | Communications and Media</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Speech Clarity | Written Expression | Speech Recognition | Near Vision | Problem Sensitivity | Deductive Reasoning | Information Ordering | Inductive Reasoning | Mathematical Reasoning | Category Flexibility | Number Facility</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Contact With Others | Importance of Being Exact or Accurate | Spend Time Sitting | Time Pressure | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Freedom to Make Decisions | Written Letters and Memos | Level of Competition | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment</t>
+  </si>
+  <si>
+    <t>Claims Adjusters, Examiners, and Investigators | Compensation, Benefits, and Job Analysis Specialists | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Customer Service Representatives | Eligibility Interviewers, Government Programs | Financial Managers | Financial Risk Specialists | Financial and Investment Analysts | Insurance Claims and Policy Processing Clerks | Insurance Underwriters | Loan Interviewers and Clerks | Loan Officers | Management Analysts | New Accounts Clerks | Personal Financial Advisors | Real Estate Sales Agents | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents</t>
+  </si>
+  <si>
+    <t>Sell life, property, casualty, health, automotive, or other types of insurance. May refer clients to independent brokers, work as an independent broker, or be employed by an insurance company.</t>
+  </si>
+  <si>
+    <t>Attend meetings, seminars, and programs to learn about new products and services, learn new skills, and receive technical assistance in developing new accounts. | Calculate premiums and establish payment method. | Call on policyholders to deliver and explain policy, to analyze insurance program and suggest additions or changes, or to change beneficiaries. | Confer with clients to obtain and provide information when claims are made on a policy. | Contact underwriter and submit forms to obtain binder coverage. | Customize insurance programs to suit individual customers, often covering a variety of risks. | Develop marketing strategies to compete with other individuals or companies who sell insurance. | Ensure that policy requirements are fulfilled, including any necessary medical examinations and the completion of appropriate forms. | Explain features, advantages, and disadvantages of various policies to promote sale of insurance plans. | Explain necessary bookkeeping requirements for customer to implement and provide group insurance program. | Inspect property, examining its general condition, type of construction, age, and other characteristics, to decide if it is a good insurance risk. | Install bookkeeping systems and resolve system problems. | Interview prospective clients to obtain data about their financial resources and needs, the physical condition of the person or property to be insured, and to discuss any existing coverage. | Monitor insurance claims to ensure they are settled equitably for both the client and the insurer. | Perform administrative tasks, such as maintaining records and handling policy renewals. | Plan and oversee incorporation of insurance program into bookkeeping system of company. | Seek out new clients and develop clientele by networking to find new customers and generate lists of prospective clients. | Select company that offers type of coverage requested by client to underwrite policy. | Sell various types of insurance policies to businesses and individuals on behalf of insurance companies, including automobile, fire, life, property, medical and dental insurance, or specialized policies, such as marine, farm/crop, and medical malpractice.</t>
+  </si>
+  <si>
+    <t>41-3031.00</t>
+  </si>
+  <si>
+    <t>Securities, Commodities, and Financial Services Sales Agents</t>
+  </si>
+  <si>
+    <t>Broker | Commodities Broker | Equity Trader | Financial Advisor | Financial Consultant | Investment Representative | Investments Advisor | Investments Specialist | Personal Banker | Trader</t>
+  </si>
+  <si>
+    <t>ADP/Vantra VOLTS | AIQ Systems TradingExpert Pro | AnalyzerXL | Aspen Graphics Technical Analysis Software | Bloomberg Professional | BondDesk Group Trader WorkStation | C++ | CQG Integrated Client | CSI Complex Systems ClientTrade | CableSoft LiveWire Trader | Calypso Technology Calypso Asset Management | Charles River Development Charles River Investment Management System | Citi The Yield Book Calculator | Customer information control system CICS | Database management software | Derivicom FinOptions XL | Email software | FileMaker Pro | Financial needs analysis software | Fixed income alternative trading systems ATS | Fund accounting software | FundCount Web | Graphics software | IBM Cognos Impromptu | IBM Notes | Imagine Software Imagine Trading System | Knight BondPoint | Leading Market Technologies EXPO | LinkedIn | Linux | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Multiple trading transaction systems | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle Java | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Siebel CRM | Python | R | Realm Business Solutions INSIGHT for ARGUS | Redi Enterprise Development Redi ERM | Regulatory agency compliance software | SAP software | Sage 50 Accounting | Sales analysis software | Salesforce software | Scheduling software | SunGard MicroHedge | Telvent DTN ProphetX | The MathWorks MATLAB | Thomson Reuters Tradeweb | Tradeweb Markets Tradeweb | Trading Blox | Triple Point Commodity XL | UNIX | Web browser software | Web-based information systems | Web-based trading systems</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Active Learning | Reading Comprehension | Speaking | Writing | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Economics and Accounting | English Language | Mathematics | Sales and Marketing | Computers and Electronics | Administration and Management | Law and Government | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Deductive Reasoning | Speech Clarity | Written Comprehension | Speech Recognition | Problem Sensitivity | Written Expression | Inductive Reasoning | Near Vision | Information Ordering | Fluency of Ideas | Category Flexibility | Mathematical Reasoning | Number Facility | Originality</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Deal With External Customers or the Public in General | Spend Time Sitting | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Level of Competition | Time Pressure</t>
+  </si>
+  <si>
+    <t>Brokerage Clerks | Business Intelligence Analysts | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Financial Managers | Financial Risk Specialists | Financial and Investment Analysts | Insurance Sales Agents | Investment Fund Managers | Loan Officers | Market Research Analysts and Marketing Specialists | New Accounts Clerks | Personal Financial Advisors | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Real Estate Brokers | Real Estate Sales Agents | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Tellers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Buy and sell securities or commodities in investment and trading firms, or provide financial services to businesses and individuals. May advise customers about stocks, bonds, mutual funds, commodities, and market conditions.</t>
+  </si>
+  <si>
+    <t>Agree on buying or selling prices at optimal levels for clients. | Buy or sell stocks, bonds, commodity futures, foreign currencies, or other securities on behalf of investment dealers. | Calculate costs for billings or commissions. | Complete sales order tickets and submit for processing of client-requested transactions. | Contact prospective customers to present information and explain available services. | Determine customers' financial services needs and prepare proposals to sell services that address these needs. | Develop financial plans, based on analysis of clients' financial status. | Devise trading, option, or hedge strategies. | Discuss financial options with clients and keep them informed about transactions. | Evaluate costs and revenue of agreements to determine continued profitability. | Explain stock market terms or trading practices to clients. | Identify opportunities or develop channels for purchase or sale of securities or commodities. | Inform other traders, managers, or customers of market conditions, including volume, price, competition, or dynamics. | Interview clients to determine clients' assets, liabilities, cash flow, insurance coverage, tax status, or financial objectives. | Keep accurate records of transactions. | Make bids or offers to buy or sell securities. | Monitor markets or positions. | Negotiate prices or contracts for securities or commodities sales or purchases. | Offer advice on the purchase or sale of particular securities. | Prepare and send requests for price quotations to all companies in a particular market. | Prepare financial reports to monitor client or corporate finances. | Price securities or commodities based on market conditions. | Purchase or sell financial derivatives for customers. | Relay buy or sell orders to securities exchanges or to firm trading departments. | Report all positions or trading results. | Review all securities transactions to ensure accuracy of information and conformance to governing agency regulations. | Sell services or equipment, such as trusts, investments, or check processing services. | Supervise support staff and ensure proper execution of contracts. | Supply the latest price quotes on any security, as well as information on the activities or financial positions of the corporations issuing these securities. | Track and analyze factors that affect price movement, such as trade policies, weather conditions, political developments, or supply and demand changes.</t>
+  </si>
+  <si>
+    <t>41-3041.00</t>
+  </si>
+  <si>
+    <t>Travel Agents</t>
+  </si>
+  <si>
+    <t>Auto Travel Counselor | Beach Expert | Corporate Travel Consultant | Destination Specialist | International Travel Consultant | Tour Coordinator | Tour Counselor | Travel Agent | Travel Consultant | Travel Counselor</t>
+  </si>
+  <si>
+    <t>Amadeus CRS | Apollo Reservation System | Colibripms Software Colibri | DataSwell | Galor Travel Booster | Global distribution system GDS software | Globekey Agentkey | IMS Travel Agent Reservation Software System | Illusions Online Illusions OnDemand | Intuit QuickBooks | MGHworld Travel Agents | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Orbitz Worldwide Orbitz for Agents | Rezdy booking software | Rezgo online booking software | Rezopia | SAP Concur | Sabre Airline Solutions SabreSonic Customer Sales &amp; Service | Sabre Central Command | TourCMS | TourWriter | Travel Agent CMS | TravelCarma | Travii reservation system software | Zoom</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Active Learning | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Sales and Marketing | Geography | Computers and Electronics | Telecommunications | Administrative | Transportation</t>
+  </si>
+  <si>
+    <t>Speech Recognition | Oral Comprehension | Speech Clarity | Written Comprehension | Oral Expression | Near Vision | Problem Sensitivity | Information Ordering | Selective Attention | Deductive Reasoning | Written Expression | Fluency of Ideas | Number Facility | Category Flexibility | Inductive Reasoning | Originality</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Spend Time Sitting | Importance of Being Exact or Accurate | Contact With Others | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Written Letters and Memos | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Level of Competition | Degree of Automation | Frequency of Decision Making | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Cargo and Freight Agents | Concierges | Counter and Rental Clerks | Customer Service Representatives | Customs Brokers | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Freight Forwarders | Hotel, Motel, and Resort Desk Clerks | Insurance Sales Agents | Meeting, Convention, and Event Planners | Real Estate Sales Agents | Receptionists and Information Clerks | Reservation and Transportation Ticket Agents and Travel Clerks | Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Telemarketers | Telephone Operators | Tour Guides and Escorts | Travel Guides</t>
+  </si>
+  <si>
+    <t>Plan and sell transportation and accommodations for customers. Determine destination, modes of transportation, travel dates, costs, and accommodations required. May also describe, plan, and arrange itineraries and sell tour packages. May assist in resolving clients' travel problems.</t>
+  </si>
+  <si>
+    <t>Book transportation and hotel reservations, using computer or telephone. | Collect payment for transportation and accommodations from customer. | Compute cost of travel and accommodations, using calculator, computer, carrier tariff books, and hotel rate books, or quote package tour's costs. | Converse with customer to determine destination, mode of transportation, travel dates, financial considerations, and accommodations required. | Plan, describe, arrange, and sell itinerary tour packages and promotional travel incentives offered by various travel carriers. | Print or request transportation carrier tickets, using computer printer system or system link to travel carrier. | Provide customer with brochures and publications containing travel information, such as local customs, points of interest, or foreign country regulations. | Record and maintain information on clients, vendors, and travel packages.</t>
+  </si>
+  <si>
+    <t>41-3091.00</t>
+  </si>
+  <si>
+    <t>Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel</t>
+  </si>
+  <si>
+    <t>Account Executive | Business Development Manager | Outside Sales Representative | Sales Account Manager | Sales Consultant | Sales Executive | Sales Representative | Service Sales Representative | Solutions Consultant | Territory Sales Manager</t>
+  </si>
+  <si>
+    <t>Apple macOS | Enterprise application integration EAI software | HubSpot software | IBM SPSS Statistics | JamBoard | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Salesforce software</t>
+  </si>
+  <si>
+    <t>Sales and Marketing | Customer and Personal Service | English Language | Administration and Management | Economics and Accounting | Communications and Media | Computers and Electronics | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Written Expression | Originality</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Level of Competition | Public Speaking | In an Enclosed Vehicle or Operate Enclosed Equipment</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Brokerage Clerks | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | First-Line Supervisors of Non-Retail Sales Workers | Insurance Sales Agents | Market Research Analysts and Marketing Specialists | Marketing Managers | New Accounts Clerks | Personal Financial Advisors | Public Relations Specialists | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Sales Engineers | Sales Managers | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Securities, Commodities, and Financial Services Sales Agents | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Sell services to individuals or businesses. May describe options or resolve client problems.</t>
+  </si>
+  <si>
+    <t>Answer customers' questions about services, prices, availability, or credit terms. | Attend sales or trade meetings or read related publications to obtain information about market conditions, business trends, regulations, or industry developments. | Compute and compare costs of services. | Consult with clients after sales or contract signings to resolve problems and provide ongoing support. | Contact prospective or existing customers to discuss how services can meet their needs. | Create forms or agreements to complete sales. | Develop sales presentations or proposals to explain service specifications. | Distribute promotional materials at meetings, conferences, or trade shows. | Emphasize or recommend service features based on knowledge of customers' needs and vendor capabilities and limitations. | Identify prospective customers using business directories, leads from clients, or information from conferences or trade shows. | Inform customers of contracts or other information pertaining to purchased services. | Maintain customer records using automated systems. | Monitor market conditions, innovations, and competitors' services, prices, and sales. | Negotiate prices or terms of sales or service agreements. | Quote prices, credit terms, contract terms, or fulfillment dates for services.</t>
+  </si>
+  <si>
+    <t>41-4011.00</t>
+  </si>
+  <si>
+    <t>Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products</t>
+  </si>
+  <si>
+    <t>Inside Sales Representative | Marketing Representative | Sales Representative</t>
+  </si>
+  <si>
+    <t>AMG Teleran SalesInSync | Act! | ActionWare | AdTrack Customer Acquisition Management CAM | Amazon Web Services AWS software | Apache Hadoop | Cegedim Target Software Target SFA Pharmaceutical Suite | Citrix cloud computing software | Enterprise application integration EAI software | FileMaker Pro | Google Ads | Google Analytics | Google Workspace software | HEAT Software GoldMine | HubSpot software | IBM InfoSphere DataStage | IBM Notes | IBM SPSS Statistics | Infor ERP SyteLine | InsideSales.com | Intuit QuickBooks | Khameleon | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | McAfee | MicroStrategy | Microsoft Access | Microsoft Azure software | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Word | NetSuite ERP | NetSuite NetCRM | NortonLifeLock cybersecurity software | Oracle Database | Oracle Fusion Applications | Oracle Hyperion | Oracle PeopleSoft | R | SAP Sybase SQL Anywhere | SAP software | SAS | Salesforce software | Salesforce.com Salesforce CRM | Scheduling software | StataCorp Stata | Tax software | Teradata Database | Virtual private networking VPN software | Voice over internet protocol VoIP system software | Web browser software | YouTube | Zoom</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Active Learning | Writing | Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | English Language | Administration and Management | Mathematics | Production and Processing | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Written Comprehension | Written Expression | Deductive Reasoning | Near Vision | Problem Sensitivity | Fluency of Ideas | Information Ordering | Inductive Reasoning | Originality | Memorization | Category Flexibility</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Time Pressure | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Level of Competition | Indoors, Environmentally Controlled | Written Letters and Memos | In an Enclosed Vehicle or Operate Enclosed Equipment | Conflict Situations | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Counter and Rental Clerks | Customer Service Representatives | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Non-Retail Sales Workers | Industrial Engineers | Industrial Production Managers | Logisticians | Parts Salespersons | Production, Planning, and Expediting Clerks | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Retail Salespersons | Sales Engineers | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Solar Sales Representatives and Assessors | Supply Chain Managers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Sell goods for wholesalers or manufacturers where technical or scientific knowledge is required in such areas as biology, engineering, chemistry, and electronics, normally obtained from at least 2 years of postsecondary education.</t>
+  </si>
+  <si>
+    <t>Advise customers on product usage to improve production. | Answer customers' questions about products, prices, availability, or credit terms. | Arrange for installation and testing of products or machinery. | Attend sales or trade meetings or read related publications to obtain information about market conditions, business trends, environmental regulations, or industry developments. | Collaborate with colleagues to exchange information, such as selling strategies or marketing information. | Complete expense reports, sales reports, or other paperwork. | Compute customer's installation or production costs and estimate savings from new services, products, or equipment. | Consult with engineers regarding technical problems with products. | Contact new or existing customers to discuss how specific products or services can meet their needs. | Demonstrate the operation or use of technical or scientific products. | Emphasize product features, based on analyses of customers' needs and on technical knowledge of product capabilities and limitations. | Identify prospective customers, using business directories, leads from existing clients, participation in organizations, or trade show or conference attendance. | Inform customers about issues related to responsible use and disposal of products, such as waste reduction or product or byproduct recycling or disposal. | Inform customers of estimated delivery schedules, service contracts, warranties, or other information pertaining to purchased products. | Initiate sales campaigns to meet sales and production expectations. | Maintain customer records, using automated systems. | Negotiate prices or terms of sales or service agreements. | Prepare and submit sales contracts for orders. | Prepare sales presentations or proposals to explain product specifications or applications. | Present information to customers about the energy efficiency or environmental impact of scientific or technical products. | Provide customers with ongoing technical support. | Provide feedback to product design teams so that products can be tailored to clients' needs. | Quote prices, credit terms, or other bid specifications. | Select or assist customers in selecting products based on customer needs, product specifications, and applicable regulations. | Sell service contracts for technical or scientific products. | Sell technical and scientific products that are environmentally sound or designed for environmental remediation. | Stock or distribute resources, such as samples or promotional or educational materials. | Study documentation or other information for new scientific or technical products. | Verify accuracy of materials lists. | Verify customer credit ratings. | Verify that delivery schedules meet project deadlines. | Visit establishments to evaluate needs or to promote product or service sales. | Visit establishments, such as pharmacies, to determine product sales.</t>
+  </si>
+  <si>
+    <t>41-4011.07</t>
+  </si>
+  <si>
+    <t>Solar Sales Representatives and Assessors</t>
+  </si>
+  <si>
+    <t>Energy Consultant | Sales Associate | Sales Consultant | Sales Representative (Sales Rep) | Salesman | Solar Consultant | Solar Energy Consultant | Solar Sales Consultant | Solar Sales Representative (Solar Sales Rep) | Solar Sales Specialist</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Autodesk AutoCAD | Google Meet | Google Workspace software | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Salesforce software | Salesforce.com Salesforce CRM | Solar analysis software | Trimble SketchUp Pro | Web browser software | Zoom</t>
+  </si>
+  <si>
+    <t>Speaking | Reading Comprehension | Active Listening | Critical Thinking | Writing | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | Design | English Language | Mathematics | Building and Construction | Administrative | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Speech Clarity | Speech Recognition | Deductive Reasoning | Problem Sensitivity | Written Expression | Near Vision | Far Vision | Information Ordering | Inductive Reasoning | Originality | Flexibility of Closure | Category Flexibility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Contact With Others | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Spend Time Sitting | Importance of Being Exact or Accurate | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Architects, Except Landscape and Naval | Architectural and Engineering Managers | Construction Managers | Cost Estimators | Electrical Engineers | Energy Auditors | Energy Engineers, Except Wind and Solar | Geothermal Production Managers | Sales Engineers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Solar Energy Installation Managers | Solar Energy Systems Engineers | Solar Photovoltaic Installers | Solar Thermal Installers and Technicians | Sustainability Specialists | Wind Energy Development Managers | Wind Energy Engineers | Wind Energy Operations Managers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Contact new or existing customers to determine their solar equipment needs, suggest systems or equipment, or estimate costs.</t>
+  </si>
+  <si>
+    <t>Assess sites to determine suitability for solar equipment, using equipment such as tape measures, compasses, and computer software. | Calculate potential solar resources or solar array production for a particular site considering issues such as climate, shading, and roof orientation. | Create customized energy management packages to satisfy customer needs. | Demonstrate use of solar and related equipment to customers or dealers. | Develop marketing or strategic plans for sales territories. | Gather information from prospective customers to identify their solar energy needs. | Generate solar energy customer leads to develop new accounts. | Prepare or review detailed design drawings, specifications, or lists related to solar installations. | Prepare proposals, quotes, contracts, or presentations for potential solar customers. | Provide customers with information, such as quotes, orders, sales, shipping, warranties, credit, funding options, incentives, or tax rebates. | Provide technical information about solar power, solar systems, equipment, and services to potential customers or dealers. | Select solar energy products, systems, or services for customers based on electrical energy requirements, site conditions, price, or other factors. | Take quote requests or orders from dealers or customers.</t>
+  </si>
+  <si>
+    <t>41-4012.00</t>
+  </si>
+  <si>
+    <t>Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products</t>
+  </si>
+  <si>
+    <t>Account Representative | Customer Account Technician | Inside Salesperson | Outside Sales Representative | Route Sales Representative | Sales Consultant | Sales Professional | Sales Representative (Sales Rep) | Salesman | Salesperson</t>
+  </si>
+  <si>
+    <t>3M Post-it App | ACT! Premium | Adobe Acrobat | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Advantage Signature Marketing Group Web Master | Airtable | Apache Groovy | Apple Keynote | Apple macOS | Aptean Onyx CRM | Ardexus Mode | Ardexus TASC | Autodesk AutoCAD | Blackboard software | Blink | Cisco Webex | Citrix cloud computing software | Commence Application Suite | Computerized call calendars | Computerized time management systems | Contact management systems | Contract Central | Contract tracking software | Data entry software | Database software | Delphi Technology | Dropbox | ESRI ArcGIS software | Eclipse IDE | Eko | Epic Systems | Evernote | Extensible markup language XML | FaceTime | Facebook | FileMaker Pro | Fund accounting software | Geographic information system GIS software | Google Ads | Google Analytics | Google Classroom | Google Docs | Google Drive | Google Meet | Google Slides | GroupMe | HEAT Software GoldMine | Handheld computer device software | Healthcare common procedure coding system HCPCS | HubSpot software | HydraNet | Hypertext markup language HTML | IBM Cognos Impromptu | IBM Notes | IBM Power Systems software | IBM SPSS Statistics | Intuit QuickBooks | LexisNexis | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MASterMind | Marketo Marketing Automation | Maximizer Software Maximizer Enterprise | McAfee | Medical condition coding software | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics CRM | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Mozilla Firefox | Mozilla Thunderbird | NetSuite ERP | NetSuite NetCRM | NortonLifeLock cybersecurity software | Novo Customer Tracking Software | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle WebLogic Server | Qlik Tech QlikView | Relational database management software | Relavis CRM Portal | Root Systems SPS Process Management | SAP Business Objects | SAP software | SAS | SSA Global BPCS | Sage 50 Accounting | Sage SalesLogix | Sales force automation software | SalesInSync | Salesforce software | SamePage StudioCRM | Screencastify | SeaMonkey | Skype | Slack | SmugMug Flickr | Social media sites | Soffront CRM Portal | Tableau | Tax software | Tigerpaw | UNIX | Virtual private networking VPN software | Voice over internet protocol VoIP system software | Yardi software | YouTube | Zoom | interlinkONE | vtiger CRM</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Reading Comprehension | Writing | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Sales and Marketing | Customer and Personal Service | English Language | Mathematics | Transportation | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Clarity | Written Comprehension | Speech Recognition | Written Expression | Near Vision | Category Flexibility | Information Ordering | Deductive Reasoning | Problem Sensitivity | Fluency of Ideas | Inductive Reasoning | Originality</t>
+  </si>
+  <si>
+    <t>Contact With Others | Telephone Conversations | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | E-Mail | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Level of Competition | Time Pressure | Importance of Being Exact or Accurate | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Buyers and Purchasing Agents, Farm Products | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Logisticians | Procurement Clerks | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Retail Salespersons | Sales Engineers | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Supply Chain Managers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Sell goods for wholesalers or manufacturers to businesses or groups of individuals. Work requires substantial knowledge of items sold.</t>
+  </si>
+  <si>
+    <t>Answer customers' questions about products, prices, availability, product uses, and credit terms. | Arrange and direct delivery and installation of products and equipment. | Check stock levels and reorder merchandise as necessary. | Consult with clients after sales or contract signings to resolve problems and to provide ongoing support. | Contact regular and prospective customers to demonstrate products, explain product features, and solicit orders. | Estimate or quote prices, credit or contract terms, warranties, and delivery dates. | Forward orders to manufacturers. | Identify prospective customers by using business directories, following leads from existing clients, participating in organizations and clubs, and attending trade shows and conferences. | Monitor market conditions, product innovations, and competitors' products, prices, and sales. | Negotiate details of contracts and payments. | Negotiate with retail merchants to improve product exposure, such as shelf positioning and advertising. | Obtain credit information about prospective customers. | Perform administrative duties, such as preparing sales budgets and reports, keeping sales records, and filing expense account reports. | Plan, assemble, and stock product displays in retail stores, or make recommendations to retailers regarding product displays, promotional programs, and advertising. | Prepare drawings, estimates, and bids that meet specific customer needs. | Prepare sales contracts and order forms. | Provide customers with product samples and catalogs. | Recommend products to customers, based on customers' needs and interests.</t>
+  </si>
+  <si>
+    <t>41-9011.00</t>
+  </si>
+  <si>
+    <t>Demonstrators and Product Promoters</t>
+  </si>
+  <si>
+    <t>Brand Ambassador | Demo Specialist (Demonstration Specialist) | Demonstrator | Event Specialist | Field Merchandiser | Food Demonstrator | In Store Demonstrator | Merchandiser | Product Ambassador | Product Demonstrator</t>
+  </si>
+  <si>
+    <t>Eko | Email software | Hypertext markup language HTML | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Social media sites | Web browser software | Zoom</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | English Language | Food Production | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Speech Clarity | Oral Comprehension | Oral Expression | Speech Recognition | Deductive Reasoning | Near Vision | Selective Attention | Category Flexibility | Information Ordering | Inductive Reasoning | Problem Sensitivity | Written Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Contact With Others | Spend Time Standing | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Time Pressure | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Physical Proximity | Spend Time Making Repetitive Motions | E-Mail | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Driver/Sales Workers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Retail Sales Workers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Marketing Managers | Meeting, Convention, and Event Planners | Merchandise Displayers and Window Trimmers | Parts Salespersons | Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Stockers and Order Fillers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Demonstrate merchandise and answer questions for the purpose of creating public interest in buying the product. May sell demonstrated merchandise.</t>
+  </si>
+  <si>
+    <t>Demonstrate or explain products, methods, or services to persuade customers to purchase products or use services. | Identify interested and qualified customers to provide them with additional information. | Instruct customers in alteration of products. | Keep areas neat while working and return items to correct locations following demonstrations. | Learn about competitors' products or consumers' interests or concerns to answer questions or provide more complete information. | Practice demonstrations to ensure that they will run smoothly. | Prepare or alter presentation contents to target specific audiences. | Provide product information, using lectures, films, charts, or slide shows. | Provide product samples, coupons, informational brochures, or other incentives to persuade people to buy products. | Recommend product or service improvements to employers. | Record and report demonstration-related information, such as the number of questions asked by the audience or the number of coupons distributed. | Research or investigate products to be presented to prepare for demonstrations. | Sell products being promoted and keep records of sales. | Set up and arrange displays or demonstration areas to attract the attention of prospective customers. | Stock shelves with products. | Suggest specific product purchases to meet customers' needs. | Train demonstrators to present a company's products or services. | Transport, assemble, and disassemble materials used in presentations. | Visit trade shows, stores, community organizations, or other venues to demonstrate products or services or to answer questions from potential customers. | Wear costumes or sign boards and walk in public to promote merchandise, services, or events. | Work as part of a team of demonstrators to accommodate large crowds.</t>
+  </si>
+  <si>
+    <t>41-9012.00</t>
+  </si>
+  <si>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>Art Class Model | Art Model | Artist's Model | Figure Model | Fine Arts Model | Life Drawing Model | Model | Nude Model | Studio Model | Undraped Artist Model</t>
+  </si>
+  <si>
+    <t>Apple Safari | Apple iOS | Facebook | Instagram | LinkedIn | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Tumblr | Twitter | Web browser software | YouTube</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Communications and Media | Fine Arts | English Language | Sales and Marketing | Design</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Near Vision | Far Vision | Gross Body Coordination | Gross Body Equilibrium | Stamina | Extent Flexibility | Memorization | Problem Sensitivity | Originality | Information Ordering | Speech Recognition | Selective Attention | Multilimb Coordination | Trunk Strength | Dynamic Flexibility</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Actors | Art Directors | Camera Operators, Television, Video, and Film | Camera and Photographic Equipment Repairers | Costume Attendants | Craft Artists | Dancers | Demonstrators and Product Promoters | Fashion Designers | Fine Artists, Including Painters, Sculptors, and Illustrators | Graphic Designers | Makeup Artists, Theatrical and Performance | Merchandise Displayers and Window Trimmers | Model Makers, Wood | Painting, Coating, and Decorating Workers | Photographers | Photographic Process Workers and Processing Machine Operators | Set and Exhibit Designers | Special Effects Artists and Animators | Talent Directors</t>
+  </si>
+  <si>
+    <t>Model garments or other apparel and accessories for prospective buyers at fashion shows, private showings, or retail establishments. May pose for photos to be used in magazines or advertisements. May pose as subject for paintings, sculptures, and other types of artistic expression.</t>
+  </si>
+  <si>
+    <t>Apply makeup to face and style hair to enhance appearance, considering such factors as color, camera techniques, and facial features. | Assemble and maintain portfolios, print composite cards, and travel to go-sees to obtain jobs. | Dress in sample or completed garments, and select accessories. | Follow strict routines of diet, sleep, and exercise to maintain appearance. | Gather information from agents concerning the pay, dates, times, provisions, and lengths of jobs. | Pose as directed, or strike suitable interpretive poses for promoting and selling merchandise or fashions during appearances, filming, or photo sessions. | Pose for artists and photographers. | Record rates of pay and durations of jobs on vouchers. | Report job completions to agencies and obtain information about future appointments. | Work closely with photographers, fashion coordinators, directors, producers, stylists, make-up artists, other models, and clients to produce the desired looks, and to finish photo shoots on schedule.</t>
+  </si>
+  <si>
+    <t>41-9021.00</t>
+  </si>
+  <si>
+    <t>Real Estate Brokers</t>
+  </si>
+  <si>
+    <t>Broker | Broker Associate | Designated Broker | Managing Broker | Real Estate Associate | Real Estate Broker | Real Estate Sales Associate | Realtor</t>
+  </si>
+  <si>
+    <t>AMTdirect | Adobe Photoshop | AppFolio Property Manager | Deep Forest Systems OnCite | Domin-8 Enterprise Solutions Tenant Pro | Enterprise Software Systems CRE Sync | Facebook | First American CoreLogic RealQuest Pro | Google Earth Pro | Intuit QuickBooks | Lease Cost Solutions LseMod | London Computer Systems Rent Manager | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Property Boulevard | Property records databases | PropertyBoss Solutions PropertyBoss | Propertyware | Real Estate Assistant REA | Real estate listing databases | RealData REIA | Salesforce software | Showing Suite real estate software | Visual Lease | Web browser software | Yardi Systems Yardi Voyager Commercial | Yardi software</t>
+  </si>
+  <si>
+    <t>Speaking | Critical Thinking | Reading Comprehension | Active Listening | Active Learning | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Sales and Marketing | Customer and Personal Service | English Language | Law and Government | Administration and Management | Economics and Accounting | Computers and Electronics | Mathematics | Communications and Media | Building and Construction | Administrative | Education and Training | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Near Vision | Speech Recognition | Speech Clarity | Written Expression | Problem Sensitivity | Inductive Reasoning | Information Ordering</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Contact With Others | In an Enclosed Vehicle or Operate Enclosed Equipment | Level of Competition | Frequency of Decision Making | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Work With or Contribute to a Work Group or Team | Written Letters and Memos | Importance of Being Exact or Accurate | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Outdoors, Exposed to All Weather Conditions | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Appraisers and Assessors of Real Estate | Appraisers of Personal and Business Property | Brokerage Clerks | Counter and Rental Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Financial and Investment Analysts | Insurance Sales Agents | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Personal Financial Advisors | Property, Real Estate, and Community Association Managers | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Real Estate Sales Agents | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Operate real estate office, or work for commercial real estate firm, overseeing real estate transactions. Other duties usually include selling real estate or renting properties and arranging loans.</t>
+  </si>
+  <si>
+    <t>Act as an intermediary in negotiations between buyers and sellers over property prices and settlement details and during the closing of sales. | Appraise property values, assessing income potential when relevant. | Arrange for financing of property purchases. | Arrange for title searches of properties being sold. | Check work completed by loan officers, attorneys, or other professionals to ensure that it is performed properly. | Compare a property with similar properties that have recently sold to determine its competitive market price. | Generate lists of properties for sale, their locations, descriptions, and available financing options, using computers. | Give buyers virtual tours of properties in which they are interested, using computers. | Maintain awareness of current income tax regulations, local zoning, building and tax laws, and growth possibilities of a property's area. | Maintain knowledge of real estate law, local economies, fair housing laws, types of available mortgages, financing options, and government programs. | Manage or operate real estate offices, handling associated business details. | Monitor fulfillment of purchase contract terms to ensure that they are handled in a timely manner. | Obtain agreements from property owners to place properties for sale with real estate firms. | Rent properties or manage rental properties. | Review property details to ensure that environmental regulations are met. | Sell, for a fee, real estate owned by others. | Supervise agents who handle real estate transactions.</t>
+  </si>
+  <si>
+    <t>41-9022.00</t>
+  </si>
+  <si>
+    <t>Real Estate Sales Agents</t>
+  </si>
+  <si>
+    <t>Real Estate Agent | Real Estate Salesperson | Realtor | Realtor Associate | Sales Agent</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Agent Business Builder | Argosy Legal Systems Power Closer | CMA Stuffers | Canva | Commercial and industrial development project cost analysis software | Corel WordPerfect Office Suite | DataBasix Technologies Lead Commander | DeLorme Topo USA | Digital contract software | DocuSign eSignature | Document creation software | Easypano Tourweaver | Email software | FaceTime | Facebook | Financial calculators software | FloodMaps | Front Desk | Fund accounting software | Garmin City Select | General Magic Portico | Geographic information system GIS software | Google Ads | Google Docs | Google Drive | Greenbrier Graphics Deed Plotter | HUD-1 software | Home rating software | IBM Lotus 1-2-3 | In-Hand Pocket APOD | Internet based MLS database software | Intuit QuickBooks | Iseemedia Photovista Panorama | Landlord Software Pro Flipper | LinkedIn | Loan application processing software | Loom | Lucero System Office Management | MediaVue | Microsoft Dynamics | Microsoft Excel | Microsoft FrontPage | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Teams | Microsoft Word | Moxi Works MoxiEngage | Moxi Works MoxiImpress | Moxi Works MoxiPresent | National Association of Realtors Online Database | Navigation software | Newsletter production software | OWL Bookkeeping for Realtors | Panorama Technologies ModelWeaver | Panoweaver Panorama | Power Real Estate Letters | PrimaSoft PC Realtor Organizer Deluxe | ProForce Highlight Flyer Master | ProForce Ultimate Brochures | RPIS Silent Flyer | Real Pro | Real estate application contract transmission REACT software | Real estate investment analysis software | RealData Comparative Lease Analysis | Reality Star ProAGENT Power Series Presentations | Realtors Property Resource RPR | RealtyStar AgentOffice | RealtyStar Real Estate Assistant | Reveal Systems Truewire | SRC Cash Flow Analyzer Pro | Scheduling software | Showing Suite HomeFeedback | Showing Suite HomeFollowup | Showing Suite Showing Calendar | Showing Suite real estate software | Social media sites | Tax software | Telluride Software Classic Trak-It | The IPIX Real Estate Wizard hometour360 Wizard | TimeValue software | TopProducer | Topaz Software Symplifi (CRM feature) | Topaz Software Symplifi (business analysis feature) | Web-administered databases | Wheatworks Real Estate Calculator Suite | Xactware Xactimate | Yardi Systems Yardi Enterprise | Yardi software | Zoom | eGrabber ListGrabber | iKorb Real Estate</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Reading Comprehension | Writing | Active Learning | Mathematics | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | English Language | Law and Government | Administrative | Administration and Management | Mathematics | Computers and Electronics | Communications and Media | Building and Construction | Economics and Accounting | Education and Training | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Written Comprehension | Written Expression | Deductive Reasoning | Category Flexibility | Information Ordering | Inductive Reasoning | Far Vision | Flexibility of Closure | Mathematical Reasoning | Problem Sensitivity | Fluency of Ideas | Near Vision</t>
+  </si>
+  <si>
+    <t>E-Mail | Contact With Others | Telephone Conversations | Level of Competition | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Time Pressure | In an Enclosed Vehicle or Operate Enclosed Equipment | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Written Letters and Memos | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Appraisers and Assessors of Real Estate | Appraisers of Personal and Business Property | Brokerage Clerks | Counter and Rental Clerks | Credit Counselors | Financial and Investment Analysts | Insurance Sales Agents | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Personal Financial Advisors | Property, Real Estate, and Community Association Managers | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Real Estate Brokers | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Rent, buy, or sell property for clients. Perform duties such as study property listings, interview prospective clients, accompany clients to property site, discuss conditions of sale, and draw up real estate contracts. Includes agents who represent buyer.</t>
+  </si>
+  <si>
+    <t>Accompany buyers during visits to and inspections of property, advising them on the suitability and value of the homes they are visiting. | Act as an intermediary in negotiations between buyers and sellers, generally representing one or the other. | Advise clients on market conditions, prices, mortgages, legal requirements, and related matters. | Advise sellers on how to make homes more appealing to potential buyers. | Answer clients' questions regarding construction work, financing, maintenance, repairs, and appraisals. | Appraise properties to determine loan values. | Arrange for title searches to determine whether clients have clear property titles. | Arrange meetings between buyers and sellers when details of transactions need to be negotiated. | Compare a property with similar properties that have recently sold to determine its competitive market price. | Conduct seminars and training sessions for sales agents to improve sales techniques. | Confer with escrow companies, lenders, home inspectors, and pest control operators to ensure that terms and conditions of purchase agreements are met before closing dates. | Contact previous clients for prospecting of referral business. | Contact property owners and advertise services to solicit property sales listings. | Contact utility companies for service hookups to clients' property. | Coordinate appointments to show homes to prospective buyers. | Coordinate property closings, overseeing signing of documents and disbursement of funds. | Develop networks of attorneys, mortgage lenders, and contractors to whom clients may be referred. | Display commercial, industrial, agricultural, and residential properties to clients and explain their features. | Evaluate mortgage options to help clients obtain financing at the best prevailing rates and terms. | Generate lists of properties that are compatible with buyers' needs and financial resources. | Inspect condition of premises, and arrange for necessary maintenance or notify owners of maintenance needs. | Interview clients to determine what kinds of properties they are seeking. | Investigate clients' financial and credit status to determine eligibility for financing. | Locate and appraise undeveloped areas for building sites, based on evaluations of area market conditions. | Prepare documents such as representation contracts, purchase agreements, closing statements, deeds, and leases. | Present purchase offers to sellers for consideration. | Promote sales of properties through advertisements, open houses, and participation in multiple listing services. | Rent or lease properties on behalf of clients. | Review plans for new construction with clients, enumerating and recommending available options and features. | Review property listings, trade journals, and relevant literature, and attend conventions, seminars, and staff and association meetings, to remain knowledgeable about real estate markets. | Secure construction or purchase financing with own firm or mortgage company. | Solicit and compile listings of available rental properties. | Visit properties to assess them before showing them to clients.</t>
+  </si>
+  <si>
+    <t>41-9031.00</t>
+  </si>
+  <si>
+    <t>Sales Engineers</t>
+  </si>
+  <si>
+    <t>Business Development Engineer | Inside Sales Engineer | Product Sales Engineer | Sales Applications Engineer | Sales Engineer | Technical Marketing Engineer | Technical Sales Engineer</t>
+  </si>
+  <si>
+    <t>Ab Initio | Amazon Web Services AWS software | Ansible software | Apache Cassandra | Apache HBase | Apache Hadoop | Apache Pig | Apache Struts | Apple iOS | Atlassian JIRA | Autodesk AutoCAD | Border Gateway Protocol BGP | C | C++ | Cisco Systems CiscoWorks | Cisco Systems VPN Client | Citrix cloud computing software | Dassault Systemes SolidWorks | Database management software | Docker | Enterprise JavaBeans | Enterprise application integration EAI software | Extensible hypertext markup language XHTML | Extensible markup language XML | Firewall software | Google Cloud software | Google Workspace software | Graphics software | Hewlett Packard HP-UX | Hyperion Solutions Hyperion System 9 Bi+ | IBM Cognos Business Intelligence | IBM Cognos Impromptu | IBM DB2 | IBM Domino | Informatica Corporation PowerCenter | JavaScript | Kubernetes | Linux | Management information systems MIS | MapReduce big data software | McAfee | MicroStrategy | MicroStrategy Desktop | Microsoft Access | Microsoft Active Directory | Microsoft Azure software | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office Live Meeting | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows Server | Microsoft Word | Network directory services software | NortonLifeLock cybersecurity software | Oracle Database | Oracle Java | Oracle PeopleSoft | Oracle Solaris | PHP | Perl | Platform as a service PaaS | Python | R | RESTful API | React | Ruby | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Business One | SAP BusinessObjects Crystal Reports | SAP software | Sales analysis software | Salesforce software | Scheduling software | Security assertion markup language SAML | Shell script | Single sign-on SSO | Software as a service SaaS | Splunk Enterprise | Structured query language SQL | Teradata Database | UNIX | Virtual private networking VPN software | Voice over internet protocol VoIP system software | Web browser software | WebEx Sales Center | Wireshark</t>
+  </si>
+  <si>
+    <t>Speaking | Critical Thinking | Reading Comprehension | Active Listening | Writing | Active Learning | Learning Strategies | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | Engineering and Technology | English Language | Mathematics | Administration and Management | Design | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Expression | Speech Clarity | Oral Comprehension | Written Comprehension | Deductive Reasoning | Inductive Reasoning | Speech Recognition | Written Expression | Problem Sensitivity | Information Ordering | Fluency of Ideas | Category Flexibility | Near Vision | Originality | Number Facility | Mathematical Reasoning | Speed of Closure | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Contact With Others | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Being Exact or Accurate | Level of Competition | Spend Time Sitting | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Architectural and Engineering Managers | Commercial and Industrial Designers | Computer Systems Analysts | Computer Systems Engineers/Architects | Electrical Engineers | Electrical and Electronic Engineering Technologists and Technicians | Electronics Engineers, Except Computer | Industrial Engineering Technologists and Technicians | Industrial Engineers | Logistics Engineers | Manufacturing Engineers | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Project Management Specialists | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Software Developers | Solar Sales Representatives and Assessors</t>
+  </si>
+  <si>
+    <t>Sell business goods or services, the selling of which requires a technical background equivalent to a baccalaureate degree in engineering.</t>
+  </si>
+  <si>
+    <t>Arrange for demonstrations or trial installations of equipment. | Attend company training seminars to become familiar with product lines. | Attend trade shows and seminars to promote products or to learn about industry developments. | Collaborate with sales teams to understand customer requirements, to promote the sale of company products, and to provide sales support. | Confer with customers and engineers to assess equipment needs and to determine system requirements. | Create sales or service contracts for products or services. | Develop sales plans to introduce products in new markets. | Develop, present, or respond to proposals for specific customer requirements, including request for proposal responses and industry-specific solutions. | Diagnose problems with installed equipment. | Document account activities, generate reports, and keep records of business transactions with customers and suppliers. | Identify resale opportunities and support them to achieve sales plans. | Keep informed on industry news and trends, products, services, competitors, relevant information about legacy, existing, and emerging technologies, and the latest product-line developments. | Maintain sales forecasting reports. | Plan and modify product configurations to meet customer needs. | Prepare and deliver technical presentations that explain products or services to customers and prospective customers. | Provide information needed for the development of custom-made machinery. | Provide technical and non-technical support and services to clients or other staff members regarding the use, operation, and maintenance of equipment. | Recommend improved materials or machinery to customers, documenting how such changes will lower costs or increase production. | Report to supervisors about prospective firms' credit ratings. | Research and identify potential customers for products or services. | Secure and renew orders and arrange delivery. | Sell products requiring extensive technical expertise and support for installation and use, such as material handling equipment, numerical-control machinery, or computer systems. | Train team members in the customer applications of technologies. | Visit prospective buyers at commercial, industrial, or other establishments to show samples or catalogs, and to inform them about product pricing, availability, and advantages. | Write technical documentation for products.</t>
+  </si>
+  <si>
+    <t>41-9041.00</t>
+  </si>
+  <si>
+    <t>Telemarketers</t>
+  </si>
+  <si>
+    <t>Call Agent | Inside Sales Representative (Inside Sales Rep) | Telemarketer | Telemarketing Sales Representative (Telemarketing Sales Rep) | Telephone Sales Representative (TSR) | Telephone Service Representative (TSR) | Telesales Representative (Telesales Rep) | Telesales Specialist</t>
+  </si>
+  <si>
+    <t>Acarda Sales Technologies Acarda Outbound | Automatic call distribution software | Database Systems Corp Telemation | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Remote access call center software | Salesforce software | Softphone software | Zoom</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Sales and Marketing | Customer and Personal Service | English Language | Administration and Management | Computers and Electronics | Communications and Media</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Written Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Spend Time Sitting | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Dealing With Unpleasant, Angry, or Discourteous People | Level of Competition | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | E-Mail | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Non-Retail Sales Workers | Market Research Analysts and Marketing Specialists | New Accounts Clerks | Order Clerks | Public Relations Specialists | Real Estate Sales Agents | Receptionists and Information Clerks | Retail Salespersons | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Securities, Commodities, and Financial Services Sales Agents | Switchboard Operators, Including Answering Service | Telephone Operators</t>
+  </si>
+  <si>
+    <t>Solicit donations or orders for goods or services over the telephone.</t>
+  </si>
+  <si>
+    <t>Adjust sales scripts to better target the needs and interests of specific individuals. | Answer telephone calls from potential customers who have been solicited through advertisements. | Conduct client or market surveys to obtain information about potential customers. | Contact businesses or private individuals by telephone to solicit sales for goods or services, or to request donations for charitable causes. | Deliver prepared sales talks, reading from scripts that describe products or services, to persuade potential customers to purchase a product or service or to make a donation. | Explain products or services and prices, and answer questions from customers. | Maintain records of contacts, accounts, and orders. | Obtain customer information such as name, address, and payment method, and enter orders into computers. | Obtain names and telephone numbers of potential customers from sources such as telephone directories, magazine reply cards, and lists purchased from other organizations. | Record names, addresses, purchases, and reactions of prospects contacted. | Schedule appointments for sales representatives to meet with prospective customers or for customers to attend sales presentations. | Telephone or write letters to respond to correspondence from customers or to follow up initial sales contacts.</t>
+  </si>
+  <si>
+    <t>41-9091.00</t>
+  </si>
+  <si>
+    <t>Door-to-Door Sales Workers, News and Street Vendors, and Related Workers</t>
+  </si>
+  <si>
+    <t>Direct Sales Coach | Door-to-Door Sales Trainer | Independent Beauty Consultant | Independent Distributor | Independent Sales Associate | Independent Sales Representative | Sales Representative (Sales Rep) | Street Vendor</t>
+  </si>
+  <si>
+    <t>Facebook | Microsoft Excel | Microsoft Office software | Route mapping software | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | English Language | Administrative | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Clarity | Speech Recognition | Written Expression | Information Ordering | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Telephone Conversations | E-Mail | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Public Speaking | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Baristas | Buyers and Purchasing Agents, Farm Products | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | Driver/Sales Workers | First-Line Supervisors of Retail Sales Workers | Merchandise Displayers and Window Trimmers | Order Clerks | Parts Salespersons | Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Sell goods or services door-to-door or on the street.</t>
+  </si>
+  <si>
+    <t>Answer questions about product features and benefits. | Arrange buying parties and solicit sponsorship of such parties to sell merchandise. | Circulate among potential customers or travel by foot, truck, automobile, or bicycle to deliver or sell merchandise or services. | Deliver merchandise and collect payment. | Develop prospect lists. | Distribute product samples or literature that details products or services. | Explain products or services and prices and demonstrate use of products. | Order or purchase supplies. | Persuade customers to purchase merchandise or services. | Set up and display sample merchandise at parties or stands. | Stock carts or stands. | Write and record orders for merchandise or enter orders into computers.</t>
+  </si>
+  <si>
+    <t>41-9099.00</t>
+  </si>
+  <si>
+    <t>Sales and Related Workers, All Other</t>
+  </si>
+  <si>
+    <t>Account Representative | Business Development Representative | Inside Sales Representative | Sales Agent | Sales Associate | Sales Consultant | Sales Coordinator | Sales Representative | Sales Specialist | Territory Representative</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Microsoft Power BI | Enterprise resource planning ERP system</t>
+  </si>
+  <si>
+    <t>Sales and Marketing | Customer and Personal Service | English Language | Administration and Management | Economics and Accounting | Computers and Electronics | Communications and Media | Mathematics</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Level of Competition | Public Speaking</t>
+  </si>
+  <si>
+    <t>Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Advertising Sales Agents | Insurance Sales Agents | Securities, Commodities, and Financial Services Sales Agents | Travel Agents | Real Estate Sales Agents | Real Estate Brokers | Sales Engineers | Telemarketers | Demonstrators and Product Promoters | Counter and Rental Clerks | Parts Salespersons | Solar Sales Representatives and Assessors | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Non-Retail Sales Workers | Sales Managers</t>
+  </si>
+  <si>
+    <t>All sales and related workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform sales duties in roles not classified separately. | Identify prospective customers through research, referrals, and outreach. | Contact prospects to present products, services, and pricing. | Assess customer needs and recommend suitable products or solutions. | Prepare and deliver sales presentations, proposals, and quotations. | Negotiate terms, pricing, and contracts within authorized limits. | Process orders and coordinate delivery, installation, and follow-up. | Maintain customer records, sales pipelines, and activity reports. | Meet or exceed assigned sales targets and performance metrics. | Resolve customer complaints and coordinate service or replacement. | Monitor competitor offerings, market conditions, and pricing trends. | Attend trade shows, product training, and industry events. | Collaborate with marketing, operations, and support teams. | Follow up with customers to build relationships and generate repeat business.</t>
+  </si>
+  <si>
+    <t>43-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Office and Administrative Support Workers</t>
+  </si>
+  <si>
+    <t>Accounting Manager | Accounts Payable Supervisor | Accounts Receivable Manager | Administrative Supervisor | Customer Service Manager | Customer Service Supervisor | Office Coordinator | Office Manager | Office Supervisor | Staff Services Manager</t>
+  </si>
+  <si>
+    <t>ADP Workforce Now | Adobe Acrobat | Apple macOS | Blackbaud The Raiser's Edge | Blackboard software | Bookkeeping software | Citrix cloud computing software | Contract management software | Data entry software | Database software | Delphi Technology | Document management system software | Dropbox | Evernote | Facebook | FileMaker Pro | Fund accounting software | Google Docs | Google Drive | GroupMe | HCSS HeavyBid | HCSS HeavyJob | Handheld computer device software | Healthcare common procedure coding system HCPCS | Henry Schein Dentrix | Human resource management software HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | IBM SPSS Statistics | Intuit QuickBooks | JamBoard | LexisNexis | LogMeIn GoToMeeting | Loom | MEDITECH software | Medical condition coding software | Medical procedure coding software | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Mozilla Firefox | Nearpod | NetSuite ERP | NortonLifeLock cybersecurity software | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Taleo | Padlet | Payroll software | Qlik Tech QlikView | Quicken | SAP Business Objects | SAP Crystal Reports | SAP software | Sage 50 Accounting | Salesforce software | Screencastify | Slack | SmugMug Flickr | Social media sites | Tableau | Tax software | Web browser software | Work scheduling software | Yardi software | YouTube</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Reading Comprehension | Critical Thinking | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Administration and Management | Customer and Personal Service | English Language | Administrative | Computers and Electronics | Personnel and Human Resources | Economics and Accounting</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Speech Recognition | Speech Clarity | Problem Sensitivity | Deductive Reasoning | Information Ordering | Near Vision | Inductive Reasoning | Originality | Fluency of Ideas | Category Flexibility | Selective Attention</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | E-Mail | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Work Outcomes and Results of Other Workers | Spend Time Sitting | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Freedom to Make Decisions | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Indoors, Environmentally Controlled | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Specialists | Management Analysts | Office Clerks, General | Project Management Specialists</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate the activities of clerical and administrative support workers.</t>
+  </si>
+  <si>
+    <t>Analyze financial activities of establishments or departments and provide input into budget planning and preparation processes. | Arrange for necessary maintenance or repair work. | Compute figures such as balances, totals, or commissions. | Consult with managers or other personnel to resolve problems in areas such as equipment performance, output quality, or work schedules. | Coordinate activities with other supervisory personnel or with other work units or departments. | Coordinate or perform activities associated with shipping, receiving, distribution, or transportation. | Design, implement, or evaluate staff training and development programs, customer service initiatives, or performance measurement criteria. | Develop or update procedures, policies, or standards. | Develop work schedules according to budgets and workloads. | Discuss job performance problems with employees to identify causes and issues and to work on resolving problems. | Evaluate employees' job performance and conformance to regulations and recommend appropriate personnel action. | Implement corporate or departmental policies, procedures, and service standards in conjunction with management. | Interpret and communicate work procedures and company policies to staff. | Keep informed of provisions of labor-management agreements and their effects on departmental operations. | Maintain records pertaining to inventory, personnel, orders, supplies, or machine maintenance. | Make recommendations to management concerning such issues as staffing decisions or procedural changes. | Monitor inventory levels and requisition or purchase supplies as needed. | Participate in the work of subordinates to facilitate productivity or to overcome difficult aspects of work. | Plan for or coordinate office services, such as equipment or supply acquisition or organization, disposal of assets, relocation, parking, maintenance, or security services. | Plan layouts of stockrooms, warehouses, or other storage areas, considering turnover, size, weight, or related factors pertaining to items stored. | Prepare and issue work schedules, deadlines, and duty assignments for office or administrative staff. | Provide employees with guidance in handling difficult or complex problems or in resolving escalated complaints or disputes. | Recruit, interview, and select employees. | Research, compile, and prepare reports, manuals, correspondence, or other information required by management or governmental agencies. | Resolve customer complaints or answer customers' questions regarding policies and procedures. | Review records or reports pertaining to activities such as production, payroll, or shipping to verify details, monitor work activities, or evaluate performance. | Supervise the work of office, administrative, or customer service employees to ensure adherence to quality standards, deadlines, and proper procedures, correcting errors or problems. | Train or instruct employees in job duties or company policies or arrange for training to be provided.</t>
+  </si>
+  <si>
+    <t>43-2011.00</t>
+  </si>
+  <si>
+    <t>Switchboard Operators, Including Answering Service</t>
+  </si>
+  <si>
+    <t>CBX Operator (Computerized Branch Exchange Operator) | Central Communications Specialist | Communications Operator | Communications Specialist | Information Specialist | PBX Operator (Private Branch Exchange Operator) | Switchboard Operator (SB Operator) | Switchboard Receptionist (SB Receptionist) | Telecommunications Clerk | Telecommunications Operator</t>
+  </si>
+  <si>
+    <t>IBM Notes | M-Tech Hotel Service Optimization System HotSOS | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Computers and Electronics | Telecommunications</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Near Vision | Selective Attention | Information Ordering | Inductive Reasoning | Deductive Reasoning | Written Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Dealing With Unpleasant, Angry, or Discourteous People | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Written Letters and Memos | Physical Proximity | Freedom to Make Decisions | Spend Time Sitting | Spend Time Making Repetitive Motions | Conflict Situations | Importance of Repeating Same Tasks | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Billing and Posting Clerks | Brokerage Clerks | Customer Service Representatives | Data Entry Keyers | Dispatchers, Except Police, Fire, and Ambulance | Executive Secretaries and Executive Administrative Assistants | First-Line Supervisors of Office and Administrative Support Workers | Mail Clerks and Mail Machine Operators, Except Postal Service | Medical Secretaries and Administrative Assistants | Office Clerks, General | Postal Service Clerks | Public Safety Telecommunicators | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Telecommunications Engineering Specialists | Telecommunications Equipment Installers and Repairers, Except Line Installers | Telemarketers | Telephone Operators | Word Processors and Typists</t>
+  </si>
+  <si>
+    <t>Operate telephone business systems equipment or switchboards to relay incoming, outgoing, and interoffice calls. May supply information to callers and record messages.</t>
+  </si>
+  <si>
+    <t>Answer incoming calls, greeting callers, providing information, transferring calls or taking messages as necessary. | Answer simple questions about clients' businesses, using reference files. | Complete forms for sales orders. | Contact security staff members when necessary, using radio-telephones. | Greet visitors, log them in and out of the facility, assign them security badges, and contact employee escorts. | Keep records of calls placed and charges incurred. | Monitor alarm systems to ensure that secure conditions are maintained. | Monitor emergency and code alarms, make emergency announcements, or route emergency calls to the appropriate location. | Operate communication systems, such as telephone, switchboard, intercom, two-way radio, or public address. | Page individuals to inform them of telephone calls, using paging or interoffice communication equipment. | Perform administrative tasks, such as accepting orders, scheduling appointments or meeting rooms, or sending and receiving faxes. | Perform various cash handling tasks, such as collecting payments, making bank deposits, or managing petty cash. | Perform various data entry or word processing tasks, such as updating phone directories, typing or proofreading documents, or creating schedules. | Place orders, such as for equipment, supplies, or catering for meetings. | Place telephone calls or arrange conference calls as instructed. | Process incoming or outgoing mail, packages, or deliveries. | Record messages, suggesting rewording for clarity or conciseness. | Relay or route written or verbal messages. | Stamp messages with time and date and file them appropriately.</t>
+  </si>
+  <si>
+    <t>43-2021.00</t>
+  </si>
+  <si>
+    <t>Telephone Operators</t>
+  </si>
+  <si>
+    <t>411 Directory Assistance Operator (411 Directory Assistance Op) | Directory Assistance Operator (Directory Assistance Op) | Information Specialist | Live Source Operator (Live Source Op) | Long Distance Operator (LD Operator) | PBX Operator (Post Box Exchange Operator) | Phone Operator (Telephone Operator) | Phone Secretary (Telephone Secretary) | TELECOM Op (Telecommunications Operator) | Toll Operator (Toll Op)</t>
+  </si>
+  <si>
+    <t>Computer aided dispatch software | Handheld computer device software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Video conference software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Telecommunications | Administrative | English Language | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Near Vision | Selective Attention | Problem Sensitivity | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Contact With Others | Telephone Conversations | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Indoors, Environmentally Controlled | Frequency of Decision Making | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Coordinate or Lead Others in Accomplishing Work Activities | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Repeating Same Tasks | Spend Time Sitting | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Cashiers | Computer Network Support Specialists | Customer Service Representatives | Data Entry Keyers | Dispatchers, Except Police, Fire, and Ambulance | File Clerks | Insurance Claims and Policy Processing Clerks | Interviewers, Except Eligibility and Loan | Medical Secretaries and Administrative Assistants | Office Clerks, General | Public Safety Telecommunicators | Receptionists and Information Clerks | Reservation and Transportation Ticket Agents and Travel Clerks | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Switchboard Operators, Including Answering Service | Telecommunications Equipment Installers and Repairers, Except Line Installers | Telemarketers | Word Processors and Typists</t>
+  </si>
+  <si>
+    <t>Provide information by accessing alphabetical, geographical, or other directories. Assist customers with special billing requests, such as charges to a third party and credits or refunds for incorrectly dialed numbers or bad connections. May handle emergency calls and assist children or people with physical disabilities to make telephone calls.</t>
+  </si>
+  <si>
+    <t>Interrupt busy lines if an emergency warrants. | Keep records of calls placed and received, and of related toll charges. | Listen to customer requests, referring to alphabetical or geographical directories to answer questions and provide telephone information. | Monitor automated systems for placing collect calls and intervene for a callers needing assistance. | Observe signal lights on switchboards, and dial or press buttons to make connections. | Offer special assistance to persons such as those who are unable to dial or who are in emergency situations. | Operate paging systems or other systems of bells or buzzers to notify recipients of incoming calls. | Operate telephone switchboards and systems to advance and complete connections, including those for local, long distance, pay telephone, mobile, person-to-person, and emergency calls. | Perform clerical duties such as typing, proofreading, and sorting mail. | Promote company products, services, and savings plans when appropriate. | Provide assistance for customers with special billing requests. | Provide relay service for users who are deaf or hard of hearing. | Suggest and check alternate spellings, locations, or listing formats to customers lacking details or complete information. | Update directory information.</t>
+  </si>
+  <si>
+    <t>43-2099.00</t>
+  </si>
+  <si>
+    <t>Communications Equipment Operators, All Other</t>
+  </si>
+  <si>
+    <t>Communications Operator | Dispatch Operator | Message Center Operator | Paging Operator | Radio Operator | Relay Operator | Teletype Operator | Communications Center Operator | Telecommunications Operator | Console Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Scheduling software</t>
+  </si>
+  <si>
+    <t>Telecommunications | Customer and Personal Service | English Language | Computers and Electronics | Communications and Media | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Auditory Attention | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Degree of Automation | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Switchboard Operators, Including Answering Service | Telephone Operators | Public Safety Telecommunicators | Dispatchers, Except Police, Fire, and Ambulance | Customer Service Representatives | Receptionists and Information Clerks | Reservation and Transportation Ticket Agents and Travel Clerks | Order Clerks | Correspondence Clerks | Data Entry Keyers | Office Clerks, General | Information and Record Clerks, All Other | Cargo and Freight Agents | Couriers and Messengers | Telemarketers | First-Line Supervisors of Office and Administrative Support Workers | Computer User Support Specialists | Telecommunications Equipment Installers and Repairers, Except Line Installers | Word Processors and Typists | Office and Administrative Support Workers, All Other</t>
+  </si>
+  <si>
+    <t>All communications equipment operators not listed separately.</t>
+  </si>
+  <si>
+    <t>Operate communications equipment in roles not classified separately. | Receive, route, and transmit voice, radio, and data communications. | Monitor communication channels and equipment status displays. | Record messages, call details, and transmission logs accurately. | Relay information promptly to appropriate personnel and units. | Operate consoles, radios, paging systems, and messaging platforms. | Follow established protocols for routine and emergency communications. | Perform basic equipment checks and report malfunctions for repair. | Maintain directories, contact lists, and call routing information. | Provide information and assistance to callers and system users. | Maintain confidentiality of sensitive communications and records. | Coordinate with technicians during system testing and maintenance. | Compile activity statistics and prepare shift reports. | Train new operators on equipment and communication procedures.</t>
+  </si>
+  <si>
+    <t>43-3011.00</t>
+  </si>
+  <si>
+    <t>Bill and Account Collectors</t>
+  </si>
+  <si>
+    <t>Account Representative | Accounts Receivable Specialist (AR Specialist) | Collection Agent | Collection Specialist | Collector | Debt Collector | Patient Access Specialist | Patient Account Representative | Telephone Collector</t>
+  </si>
+  <si>
+    <t>ADP Drive DMS for Accounting | ADS Advantage | Adtec Agency Manager | Austin Logistics CallSelect | CU Connect processing software | Collection Data Systems CollectOne-Tiger | Columbia Ultimate Archive | Columbia Ultimate RPCS | Columbia Ultimate Remit | Data-Tel Ceasar | Debt account management and collection software | Diagnostic and procedural coding software | Document management system software | HMS | Healthcare common procedure coding system HCPCS | Intuit QuickBooks | LexisNexis | LexisNexis Banko | MEDITECH software | Medical condition coding software | Medical procedure coding software | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Ontario Systems FACS | Optical character recognition OCR software | Oracle JD Edwards EnterpriseOne | Quantrax Intelec | Relational database software | SAP software | Sage 50 Accounting | System Innovators | TCI XML Credit Interface | W3 Data BatchAppend411 | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Writing | Reading Comprehension | Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Mathematics | Economics and Accounting | Law and Government | Computers and Electronics | Administrative | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Speech Recognition | Speech Clarity | Written Expression | Near Vision | Selective Attention | Category Flexibility | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Contact With Others | Indoors, Environmentally Controlled | Spend Time Sitting | Dealing With Unpleasant, Angry, or Discourteous People | Telephone Conversations | Importance of Repeating Same Tasks | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | E-Mail | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Written Letters and Memos | Conflict Situations | Level of Competition | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Accountants and Auditors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Correspondence Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Customer Service Representatives | Financial Managers | Insurance Claims and Policy Processing Clerks | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Order Clerks | Payroll and Timekeeping Clerks | Personal Financial Advisors | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Tax Examiners and Collectors, and Revenue Agents | Tellers</t>
+  </si>
+  <si>
+    <t>Locate and notify customers of delinquent accounts by mail, telephone, or personal visit to solicit payment. Duties include receiving payment and posting amount to customer's account, preparing statements to credit department if customer fails to respond, initiating repossession proceedings or service disconnection, and keeping records of collection and status of accounts.</t>
+  </si>
+  <si>
+    <t>Advise customers of necessary actions and strategies for debt repayment. | Answer customer questions regarding problems with their accounts. | Arrange for debt repayment or establish repayment schedules, based on customers' financial situations. | Confer with customers by telephone or in person to determine reasons for overdue payments and to review the terms of sales, service, or credit contracts. | Contact insurance companies to check on status of claims payments and write appeal letters for denial on claims. | Locate and monitor overdue accounts, using computers and a variety of automated systems. | Locate and notify customers of delinquent accounts by mail, telephone, or personal visits to solicit payment. | Negotiate credit extensions when necessary. | Notify credit departments, order merchandise repossession or service disconnection, and turn over account records to attorneys when customers fail to respond to collection attempts. | Perform various administrative functions for assigned accounts, such as recording address changes and purging the records of deceased customers. | Persuade customers to pay amounts due on credit accounts, damage claims, or nonpayable checks, or to return merchandise. | Receive payments and post amounts paid to customer accounts. | Record information about financial status of customers and status of collection efforts. | Sort and file correspondence and perform miscellaneous clerical duties, such as answering correspondence and writing reports. | Trace delinquent customers to new addresses by inquiring at post offices, telephone companies, credit bureaus, or through the questioning of neighbors.</t>
+  </si>
+  <si>
+    <t>43-3021.00</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks</t>
+  </si>
+  <si>
+    <t>Account Services Representative (Accounts Services Rep) | Biller | Billing Clerk | Billing Coordinator | Item Processing Clerk (IP Clerk) | Medical Biller | Pre-Audit Clerk | Statement Clerk | Statement Distribution Clerk | Statement Services Representative (Statement Services Rep)</t>
+  </si>
+  <si>
+    <t>Accuity EPICWare | Aderant legal software | Allscripts Professional PM | Automated billing software | CAI Software Seasoft | Check imaging software | Check processing software | Check sorting control software | Database software | Epic Systems | File management systems | Fiserv PEP+ reACH | GE Healthcare Centricity EMR | Healthcare common procedure coding system HCPCS | HelpIT Systems addressIT | IBM Cognos Impromptu | IPS of Boston DoubleCheck | Image Deposit Exchange Check Station | Image exchange networks | Image replacement document IRD printing software | Intuit QuickBooks | MEDITECH software | Medical billing software | Medical condition coding software | Medical procedure coding software | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | Mitek Systems ImageNet Payments | NetSuite ERP | Optical character recognition OCR software | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft Financials | Positive pay software | Practice management software PMS | Prime Clinical | QuoteWerks | Remote deposit capture software | SAP software | Sage 50 Accounting | Sage Medical Manager | Thomson Reuters Elite Enterprise | VECTORsgi Check Management Solution | VECTORsgi Image Exchange Solution | Web browser software | eMDs Medisoft</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Mathematics | Active Listening | Speaking | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Administrative | Customer and Personal Service | English Language | Economics and Accounting | Mathematics | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Near Vision | Written Comprehension | Information Ordering | Oral Expression | Speech Recognition | Written Expression | Oral Comprehension | Problem Sensitivity | Speech Clarity | Number Facility | Category Flexibility | Deductive Reasoning | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Spend Time Sitting | Importance of Repeating Same Tasks | Contact With Others | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Written Letters and Memos | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Accountants and Auditors | Bill and Account Collectors | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Correspondence Clerks | Credit Authorizers, Checkers, and Clerks | Customer Service Representatives | File Clerks | Financial Managers | First-Line Supervisors of Office and Administrative Support Workers | Insurance Claims and Policy Processing Clerks | Office Clerks, General | Order Clerks | Payroll and Timekeeping Clerks | Postal Service Clerks | Procurement Clerks | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Shipping, Receiving, and Inventory Clerks | Tax Examiners and Collectors, and Revenue Agents | Tellers</t>
+  </si>
+  <si>
+    <t>Compile, compute, and record billing, accounting, statistical, and other numerical data for billing purposes. Prepare billing invoices for services rendered or for delivery or shipment of goods.</t>
+  </si>
+  <si>
+    <t>Answer inquiries regarding rates, routing, or procedures. | Compare previously prepared bank statements with canceled checks and reconcile discrepancies. | Compile reports of cost factors, such as labor, production, storage, and equipment. | Compute credit terms, discounts, shipment charges, or rates for goods or services to complete billing documents. | Consult sources, such as rate books, manuals, or insurance company representatives, to determine specific charges or information such as rules, regulations, or government tax and tariff information. | Contact customers to obtain or relay account information. | Create billing documents, shipping labels, credit memorandums, or credit forms. | Encode and cancel checks, using bank machines. | Fix minor problems, such as equipment jams, and notify repair personnel of major equipment problems. | Keep records of invoices and support documents. | Load machines with statements, cancelled checks, or envelopes to prepare statements for distribution to customers or stuff envelopes by hand. | Monitor equipment to ensure proper operation. | Operate typing, adding, calculating, or billing machines. | Perform bookkeeping work, including posting data or keeping other records concerning costs of goods or services or the shipment of goods. | Perform general administrative tasks, such as answering telephones, scheduling appointments, and ordering supplies or equipment. | Post stop-payment notices to prevent payment of protested checks. | Prepare itemized statements, bills, or invoices and record amounts due for items purchased or services rendered. | Resolve discrepancies in accounting records. | Return checks to customers or retrieve checks returned to customers in error, adjusting accounts and answering inquiries about errors as necessary. | Review compiled data on operating costs and revenues to set rates. | Review documents, such as purchase orders, sales tickets, charge slips, or hospital records, to compute fees or charges due. | Route statements for mailing or over-the-counter delivery to customers. | Take orders for imprinted checks. | Track accumulated hours and dollar amounts charged to each client job to calculate client fees for professional services, such as legal or accounting services. | Update manuals when rates, rules, or regulations are amended. | Verify accuracy of billing data and revise any errors. | Verify signatures and required information on checks. | Weigh envelopes containing statements to determine correct postage and affix postage, using stamps or metering equipment.</t>
+  </si>
+  <si>
+    <t>43-3031.00</t>
+  </si>
+  <si>
+    <t>Bookkeeping, Accounting, and Auditing Clerks</t>
+  </si>
+  <si>
+    <t>Account Clerk | Accounting Assistant | Accounting Associate | Accounting Clerk | Accounting Specialist | Accounting Technician | Accounts Payable Clerk | Accounts Payable Specialist | Accounts Payables Clerk | Accounts Receivable Clerk</t>
+  </si>
+  <si>
+    <t>ACS Technologies ACS Financial Suite | ADP Pay eXpert | ADP Workforce Now | AMS Services AMS Sagitta | ATX Total Accounting Office | ATX Total Engagement Office | Accounts payable software | Accounts receivable software | Accurate NXG | AcornSystems Corporate Performance Management | Act! | Activant Solutions Activant Prophet 21 | AdaptaSoft CyberPay | Adobe Acrobat | Advanced Management Systems Software for Wineries | American HealthTech Financial | Asset management software | AuditWare financial reporting and auditing software | Auditing software | Automation Counselors municiPAL | BLS Software Invoice! | Best MIP Fund Accounting | Blackbaud The Financial Edge | Blackbaud The Raiser's Edge | Business performance management BPM software | CCIS AccountAbility | CYMA IV Accounting for Windows | Cartesis ES Magnitude | ComputerEase construction accounting software | Corporate Responsibility System Technologies Limited CRSTL Compliance Positioning System | Cost accounting software | Customer information control system CICS | Data entry software | Database software | Delphi Technology | Document management system software | Dropbox | Epic Systems | FaceTime | Fifth Walk BillingTracker | FileMaker Pro | Financial compliance software | Financial reporting software | Financial statement software | FlexiFinancials FlexiLedger | Fund accounting software | General ledger software | Google Docs | Google Drive | HCSS HeavyBid | HCSS HeavyJob | HMS | Healthcare common procedure coding system HCPCS | Heron CrossTie General Ledger | Human resource management software HRMS | IBM Cognos Impromptu | IBM Notes | Infor Global Solutions Starbuilder | Intrax ProcedureNet | Intuit QuickBooks | Iron Mountain Accutrac records management software | LexisNexis | MEDITECH software | Medical condition coding software | Medical procedure coding software | MethodWare ProAudit Advisor | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Windows | Microsoft Word | NetSuite ERP | New Millennium Communications Genesis Accounting | OmniRIM Records Management Suite | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | PROPHIX Enterprise | Paisley AutoAudit | Paisley Cardmap | Paisley Focus Control Assurance | Paisley IssueTrack | Paisley RiskNavigator | Payroll software | Pentana audit work system PAWS | Quicken | RSM McGladrey Advanced Practice Solutions Paperless Audit | RSM McGladrey Auditor Assistant | Records management software | Roundtable Software Advantage Accounting System | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Concur | SAP Crystal Reports | SAP software | Sage 100 Contractor | Sage 100 ERP | Sage 50 Accounting | Sage EDP Payroll Tax | Skype | Softrax Revenue Management | Tax software | Tumbleweed SecureTransport | UA Business Software Professional Edition | Yardi software</t>
+  </si>
+  <si>
+    <t>Mathematics | Critical Thinking | Active Listening | Reading Comprehension | Writing | Speaking | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administrative | Mathematics | English Language | Economics and Accounting | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Mathematical Reasoning | Near Vision | Written Comprehension | Written Expression | Number Facility | Problem Sensitivity | Oral Expression | Speech Recognition | Category Flexibility | Information Ordering | Inductive Reasoning | Speech Clarity | Selective Attention | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>E-Mail | Indoors, Environmentally Controlled | Telephone Conversations | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Spend Time Sitting | Spend Time Making Repetitive Motions | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Time Pressure | Determine Tasks, Priorities and Goals | Written Letters and Memos | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Accountants and Auditors | Bill and Account Collectors | Billing and Posting Clerks | Brokerage Clerks | Correspondence Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | File Clerks | Financial Managers | Insurance Claims and Policy Processing Clerks | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Office Clerks, General | Payroll and Timekeeping Clerks | Securities, Commodities, and Financial Services Sales Agents | Statistical Assistants | Tax Examiners and Collectors, and Revenue Agents | Tax Preparers | Tellers</t>
+  </si>
+  <si>
+    <t>Compute, classify, and record numerical data to keep financial records complete. Perform any combination of routine calculating, posting, and verifying duties to obtain primary financial data for use in maintaining accounting records. May also check the accuracy of figures, calculations, and postings pertaining to business transactions recorded by other workers.</t>
+  </si>
+  <si>
+    <t>Access computerized financial information to answer general questions as well as those related to specific accounts. | Calculate and prepare checks for utilities, taxes, and other payments. | Calculate costs of materials, overhead, and other expenses, based on estimates, quotations and price lists. | Calculate, prepare, and issue bills, invoices, account statements, and other financial statements according to established procedures. | Check figures, postings, and documents for correct entry, mathematical accuracy, and proper codes. | Classify, record, and summarize numerical and financial data to compile and keep financial records, using journals and ledgers or computers. | Code documents according to company procedures. | Compare computer printouts to manually maintained journals to determine if they match. | Compile budget data and documents, based on estimated revenues and expenses and previous budgets. | Compile statistical, financial, accounting, or auditing reports and tables pertaining to such matters as cash receipts, expenditures, accounts payable and receivable, and profits and losses. | Complete and submit tax forms and returns, workers' compensation forms, pension contribution forms, and other government documents. | Comply with federal, state, and company policies, procedures, and regulations. | Debit, credit, and total accounts on computer spreadsheets and databases, using specialized accounting software. | Maintain inventory records. | Match order forms with invoices, and record the necessary information. | Monitor status of loans and accounts to ensure that payments are up to date. | Operate 10-key calculators, typewriters, and copy machines to perform calculations and produce documents. | Operate computers programmed with accounting software to record, store, and analyze information. | Perform financial calculations, such as amounts due, interest charges, balances, discounts, equity, and principal. | Perform general office duties, such as filing, answering telephones, and handling routine correspondence. | Prepare and process payroll information. | Prepare bank deposits by compiling data from cashiers, verifying and balancing receipts, and sending cash, checks, or other forms of payment to banks. | Prepare purchase orders and expense reports. | Prepare trial balances of books. | Receive, record, and bank cash, checks, and vouchers. | Reconcile or note and report discrepancies found in records. | Reconcile records of bank transactions. | Transfer details from separate journals to general ledgers or data processing sheets.</t>
+  </si>
+  <si>
+    <t>43-3041.00</t>
+  </si>
+  <si>
+    <t>Gambling Cage Workers</t>
+  </si>
+  <si>
+    <t>Cage Cashier | Cage and Players Club Rep (Cage and Players Club Representative) | Casino Cage Cashier | Casino Cashier | Casino Services Rep (Casino Services Representative) | Dual Rate Banker | Gaming Cage Worker | Gaming Cashier | Mutuel Clerk | Vault Cashier</t>
+  </si>
+  <si>
+    <t>Corel WordPerfect Office Suite | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Mathematics | Monitoring | Critical Thinking | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mathematics | English Language | Administration and Management | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Speech Clarity | Problem Sensitivity | Mathematical Reasoning | Number Facility | Deductive Reasoning | Information Ordering | Speech Recognition | Written Comprehension | Selective Attention | Inductive Reasoning | Written Expression</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Contact With Others | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Physical Proximity | Spend Time Standing | Frequency of Decision Making | Consequence of Error | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Cashiers | Coin, Vending, and Amusement Machine Servicers and Repairers | Counter and Rental Clerks | Credit Authorizers, Checkers, and Clerks | First-Line Supervisors of Gambling Services Workers | Gambling Change Persons and Booth Cashiers | Gambling Dealers | Gambling Managers | Gambling Surveillance Officers and Gambling Investigators | Gambling and Sports Book Writers and Runners | Hotel, Motel, and Resort Desk Clerks | New Accounts Clerks | Payroll and Timekeeping Clerks | Pharmacy Aides | Retail Salespersons | Stockers and Order Fillers | Tellers</t>
+  </si>
+  <si>
+    <t>In a gambling establishment, conduct financial transactions for patrons. Accept patron's credit application and verify credit references to provide check-cashing authorization or to establish house credit accounts. May reconcile daily summaries of transactions to balance books. May sell gambling chips, tokens, or tickets to patrons, or to other workers for resale to patrons. May convert gambling chips, tokens, or tickets to currency upon patron's request. May use a cash register or computer to record transaction.</t>
+  </si>
+  <si>
+    <t>Cash checks and process credit card advances for patrons. | Convert gaming checks, coupons, tokens, or coins to currency for gaming patrons. | Count funds and reconcile daily summaries of transactions to balance books. | Determine cash requirements for windows and order all necessary currency, coins, or chips. | Establish new computer accounts. | Follow all gaming regulations. | Maintain cage security. | Maintain confidentiality of customers' transactions. | Perform removal and rotation of cash, coin, or chip inventories as necessary. | Prepare bank deposits, balancing assigned funds as necessary. | Prepare reports, including assignment of company funds or recording of department revenues. | Provide assistance in the training and orientation of new cashiers. | Provide customers with information about casino operations. | Record casino exchange transactions, using cash registers. | Sell gambling chips, tokens, or tickets to patrons or to other workers for resale to patrons. | Supply currency, coins, chips, or gaming checks to other departments as needed. | Verify accuracy of reports, such as authorization forms, transaction reconciliations, or exchange summary reports.</t>
+  </si>
+  <si>
+    <t>43-3051.00</t>
+  </si>
+  <si>
+    <t>Payroll and Timekeeping Clerks</t>
+  </si>
+  <si>
+    <t>Payroll Assistant | Payroll Clerk | Payroll Coordinator | Payroll Representative | Payroll Specialist | Payroll Technician | Personnel Assistant | Personnel Technician | Timekeeper</t>
+  </si>
+  <si>
+    <t>ADP Enterprise HR | ADP PC/Payroll | ADP Workforce Now | ADP eTIME | API Navigator | Asure Software HCM | Automated payroll software | Automated timekeeping software | BMH Open4 Payroll | BSI ComplianceFactory | CyberShift Workforce Management 3G Time and Attendance | Data entry software | EBS On Line InstaPay | Email software | Fund accounting software | Galaxy Technologies TimeStar Enterprise | Human Resource MicroSystems HR Entre | Human resource management software HRMS | IBM Cognos Impromptu | IBM Notes | Intuit QuickBooks | Jantek Jupiter Time Attendance | Kronos Workforce Payroll | Kronos Workforce Timekeeper | MicroFocus GroupWise | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Great Plains Personal Data Keeper | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Netscape Navigator | NuView EBS | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle HRIS | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Payroll for North America | PDS Vista | PayData Advanced HR | Paychex payroll software | Payroll software | Penta software | Quicken | RSM McGladrey Clear Pay | SAP Americas mySAP ERP Human Capital Management HCM | SAP Crystal Reports | SAP software | Sage 50 Accounting | Sage HRMS | Tax software | TimePlus Payroll | UNITIME | Ultimate Software UltiPro Workplace | Virtual Software Virtual Timecard | Web browser software | WorkForce Software EmpCenter Time and Attendance | Workday software | isolved Time</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Mathematics | Writing | Speaking | Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Administrative | Mathematics | English Language | Economics and Accounting | Personnel and Human Resources | Administration and Management | Customer and Personal Service | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Written Expression | Near Vision | Oral Expression | Mathematical Reasoning | Number Facility | Information Ordering | Problem Sensitivity | Inductive Reasoning | Deductive Reasoning | Speech Clarity | Speech Recognition | Selective Attention</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Sitting | Telephone Conversations | E-Mail | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Time Pressure | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Contact With Others | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Accountants and Auditors | Administrative Services Managers | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Budget Analysts | Compensation and Benefits Managers | Compensation, Benefits, and Job Analysis Specialists | Credit Authorizers, Checkers, and Clerks | Eligibility Interviewers, Government Programs | Executive Secretaries and Executive Administrative Assistants | File Clerks | Financial Managers | First-Line Supervisors of Office and Administrative Support Workers | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Specialists | Office Clerks, General | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Tax Examiners and Collectors, and Revenue Agents | Tax Preparers | Treasurers and Controllers</t>
+  </si>
+  <si>
+    <t>Compile and record employee time and payroll data. May compute employees' time worked, production, and commission. May compute and post wages and deductions, or prepare paychecks.</t>
+  </si>
+  <si>
+    <t>Balance cash and payroll accounts. | Compile employee time, production, and payroll data from time sheets and other records. | Compile statistical reports, statements, and summaries related to pay and benefits accounts, and submit them to appropriate departments. | Complete time sheets showing employees' arrival and departure times. | Complete, verify, and process forms and documentation for administration of benefits, such as pension plans, and unemployment and medical insurance. | Compute wages and deductions, and enter data into computers. | Conduct verifications of employment. | Coordinate special programs, such as United Way campaigns, that involve payroll deductions. | Distribute and collect timecards each pay period. | Issue and record adjustments to pay related to previous errors or retroactive increases. | Keep informed about changes in tax and deduction laws that apply to the payroll process. | Keep track of leave time, such as vacation, personal, and sick leave, for employees. | Prepare and balance period-end reports, and reconcile issued payrolls to bank statements. | Prepare and file payroll tax returns. | Process and issue employee paychecks and statements of earnings and deductions. | Process paperwork for new employees and enter employee information into the payroll system. | Provide information to employees and managers on payroll matters, tax issues, benefit plans, and collective agreement provisions. | Record employee information, such as exemptions, transfers, and resignations, to maintain and update payroll records. | Review time sheets, work charts, wage computation, and other information to detect and reconcile payroll discrepancies. | Train employees on organizations' timekeeping systems. | Verify attendance, hours worked, and pay adjustments, and post information onto designated records.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1961,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" t="s">
+        <v>106</v>
+      </c>
+      <c r="K10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" t="s">
+        <v>117</v>
+      </c>
+      <c r="K11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H14" t="s">
+        <v>147</v>
+      </c>
+      <c r="I14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J14" t="s">
+        <v>149</v>
+      </c>
+      <c r="K14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" t="s">
+        <v>157</v>
+      </c>
+      <c r="H15" t="s">
+        <v>158</v>
+      </c>
+      <c r="I15" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" t="s">
+        <v>160</v>
+      </c>
+      <c r="K15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" t="s">
+        <v>167</v>
+      </c>
+      <c r="G16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" t="s">
+        <v>169</v>
+      </c>
+      <c r="I16" t="s">
+        <v>170</v>
+      </c>
+      <c r="J16" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" t="s">
+        <v>176</v>
+      </c>
+      <c r="E17" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" t="s">
+        <v>178</v>
+      </c>
+      <c r="G17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H17" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" t="s">
+        <v>181</v>
+      </c>
+      <c r="J17" t="s">
+        <v>182</v>
+      </c>
+      <c r="K17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" t="s">
+        <v>190</v>
+      </c>
+      <c r="H18" t="s">
+        <v>191</v>
+      </c>
+      <c r="I18" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" t="s">
+        <v>193</v>
+      </c>
+      <c r="K18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G19" t="s">
+        <v>201</v>
+      </c>
+      <c r="H19" t="s">
+        <v>202</v>
+      </c>
+      <c r="I19" t="s">
+        <v>203</v>
+      </c>
+      <c r="J19" t="s">
+        <v>204</v>
+      </c>
+      <c r="K19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" t="s">
+        <v>213</v>
+      </c>
+      <c r="I20" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H21" t="s">
+        <v>222</v>
+      </c>
+      <c r="I21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J21" t="s">
+        <v>224</v>
+      </c>
+      <c r="K21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" t="s">
+        <v>231</v>
+      </c>
+      <c r="G22" t="s">
+        <v>232</v>
+      </c>
+      <c r="H22" t="s">
+        <v>233</v>
+      </c>
+      <c r="I22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J22" t="s">
+        <v>235</v>
+      </c>
+      <c r="K22" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" t="s">
+        <v>188</v>
+      </c>
+      <c r="F23" t="s">
+        <v>241</v>
+      </c>
+      <c r="G23" t="s">
+        <v>242</v>
+      </c>
+      <c r="H23" t="s">
+        <v>243</v>
+      </c>
+      <c r="I23" t="s">
+        <v>244</v>
+      </c>
+      <c r="J23" t="s">
+        <v>245</v>
+      </c>
+      <c r="K23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" t="s">
+        <v>249</v>
+      </c>
+      <c r="D24" t="s">
+        <v>250</v>
+      </c>
+      <c r="E24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F24" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" t="s">
+        <v>253</v>
+      </c>
+      <c r="H24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I24" t="s">
+        <v>255</v>
+      </c>
+      <c r="J24" t="s">
+        <v>256</v>
+      </c>
+      <c r="K24" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" t="s">
+        <v>260</v>
+      </c>
+      <c r="D25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" t="s">
+        <v>262</v>
+      </c>
+      <c r="F25" t="s">
+        <v>263</v>
+      </c>
+      <c r="G25" t="s">
+        <v>264</v>
+      </c>
+      <c r="H25" t="s">
+        <v>265</v>
+      </c>
+      <c r="I25" t="s">
+        <v>266</v>
+      </c>
+      <c r="J25" t="s">
+        <v>267</v>
+      </c>
+      <c r="K25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B26" t="s">
+        <v>270</v>
+      </c>
+      <c r="C26" t="s">
+        <v>271</v>
+      </c>
+      <c r="D26" t="s">
+        <v>272</v>
+      </c>
+      <c r="E26" t="s">
+        <v>273</v>
+      </c>
+      <c r="F26" t="s">
+        <v>274</v>
+      </c>
+      <c r="G26" t="s">
+        <v>275</v>
+      </c>
+      <c r="H26" t="s">
+        <v>276</v>
+      </c>
+      <c r="I26" t="s">
+        <v>277</v>
+      </c>
+      <c r="J26" t="s">
+        <v>278</v>
+      </c>
+      <c r="K26" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>280</v>
+      </c>
+      <c r="B27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C27" t="s">
+        <v>282</v>
+      </c>
+      <c r="D27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E27" t="s">
+        <v>284</v>
+      </c>
+      <c r="F27" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" t="s">
+        <v>286</v>
+      </c>
+      <c r="H27" t="s">
+        <v>287</v>
+      </c>
+      <c r="I27" t="s">
+        <v>288</v>
+      </c>
+      <c r="J27" t="s">
+        <v>289</v>
+      </c>
+      <c r="K27" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>291</v>
+      </c>
+      <c r="B28" t="s">
+        <v>292</v>
+      </c>
+      <c r="C28" t="s">
+        <v>293</v>
+      </c>
+      <c r="D28" t="s">
+        <v>294</v>
+      </c>
+      <c r="E28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F28" t="s">
+        <v>296</v>
+      </c>
+      <c r="G28" t="s">
+        <v>297</v>
+      </c>
+      <c r="H28" t="s">
+        <v>298</v>
+      </c>
+      <c r="I28" t="s">
+        <v>299</v>
+      </c>
+      <c r="J28" t="s">
+        <v>300</v>
+      </c>
+      <c r="K28" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>302</v>
+      </c>
+      <c r="B29" t="s">
+        <v>303</v>
+      </c>
+      <c r="C29" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" t="s">
+        <v>305</v>
+      </c>
+      <c r="E29" t="s">
+        <v>306</v>
+      </c>
+      <c r="F29" t="s">
+        <v>307</v>
+      </c>
+      <c r="G29" t="s">
+        <v>308</v>
+      </c>
+      <c r="H29" t="s">
+        <v>309</v>
+      </c>
+      <c r="I29" t="s">
+        <v>310</v>
+      </c>
+      <c r="J29" t="s">
+        <v>311</v>
+      </c>
+      <c r="K29" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" t="s">
+        <v>314</v>
+      </c>
+      <c r="C30" t="s">
+        <v>315</v>
+      </c>
+      <c r="D30" t="s">
+        <v>316</v>
+      </c>
+      <c r="E30" t="s">
+        <v>188</v>
+      </c>
+      <c r="F30" t="s">
+        <v>317</v>
+      </c>
+      <c r="G30" t="s">
+        <v>318</v>
+      </c>
+      <c r="H30" t="s">
+        <v>319</v>
+      </c>
+      <c r="I30" t="s">
+        <v>320</v>
+      </c>
+      <c r="J30" t="s">
+        <v>321</v>
+      </c>
+      <c r="K30" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" t="s">
+        <v>324</v>
+      </c>
+      <c r="C31" t="s">
+        <v>325</v>
+      </c>
+      <c r="D31" t="s">
+        <v>326</v>
+      </c>
+      <c r="E31" t="s">
+        <v>327</v>
+      </c>
+      <c r="F31" t="s">
+        <v>328</v>
+      </c>
+      <c r="G31" t="s">
+        <v>329</v>
+      </c>
+      <c r="H31" t="s">
+        <v>330</v>
+      </c>
+      <c r="I31" t="s">
+        <v>331</v>
+      </c>
+      <c r="J31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K31" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" t="s">
+        <v>335</v>
+      </c>
+      <c r="C32" t="s">
+        <v>336</v>
+      </c>
+      <c r="D32" t="s">
+        <v>337</v>
+      </c>
+      <c r="E32" t="s">
+        <v>338</v>
+      </c>
+      <c r="F32" t="s">
+        <v>339</v>
+      </c>
+      <c r="G32" t="s">
+        <v>340</v>
+      </c>
+      <c r="H32" t="s">
+        <v>341</v>
+      </c>
+      <c r="I32" t="s">
+        <v>342</v>
+      </c>
+      <c r="J32" t="s">
+        <v>343</v>
+      </c>
+      <c r="K32" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>345</v>
+      </c>
+      <c r="B33" t="s">
+        <v>346</v>
+      </c>
+      <c r="C33" t="s">
+        <v>347</v>
+      </c>
+      <c r="D33" t="s">
+        <v>348</v>
+      </c>
+      <c r="E33" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" t="s">
+        <v>350</v>
+      </c>
+      <c r="G33" t="s">
+        <v>351</v>
+      </c>
+      <c r="H33" t="s">
+        <v>352</v>
+      </c>
+      <c r="I33" t="s">
+        <v>353</v>
+      </c>
+      <c r="J33" t="s">
+        <v>354</v>
+      </c>
+      <c r="K33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>356</v>
+      </c>
+      <c r="B34" t="s">
+        <v>357</v>
+      </c>
+      <c r="C34" t="s">
+        <v>358</v>
+      </c>
+      <c r="D34" t="s">
+        <v>359</v>
+      </c>
+      <c r="E34" t="s">
+        <v>360</v>
+      </c>
+      <c r="F34" t="s">
+        <v>361</v>
+      </c>
+      <c r="G34" t="s">
+        <v>362</v>
+      </c>
+      <c r="H34" t="s">
+        <v>363</v>
+      </c>
+      <c r="I34" t="s">
+        <v>364</v>
+      </c>
+      <c r="J34" t="s">
+        <v>365</v>
+      </c>
+      <c r="K34" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>367</v>
+      </c>
+      <c r="B35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" t="s">
+        <v>369</v>
+      </c>
+      <c r="D35" t="s">
+        <v>370</v>
+      </c>
+      <c r="E35" t="s">
+        <v>371</v>
+      </c>
+      <c r="F35" t="s">
+        <v>372</v>
+      </c>
+      <c r="G35" t="s">
+        <v>373</v>
+      </c>
+      <c r="H35" t="s">
+        <v>374</v>
+      </c>
+      <c r="I35" t="s">
+        <v>375</v>
+      </c>
+      <c r="J35" t="s">
+        <v>376</v>
+      </c>
+      <c r="K35" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>378</v>
+      </c>
+      <c r="B36" t="s">
+        <v>379</v>
+      </c>
+      <c r="C36" t="s">
+        <v>380</v>
+      </c>
+      <c r="D36" t="s">
+        <v>381</v>
+      </c>
+      <c r="E36" t="s">
+        <v>382</v>
+      </c>
+      <c r="F36" t="s">
+        <v>383</v>
+      </c>
+      <c r="G36" t="s">
+        <v>384</v>
+      </c>
+      <c r="H36" t="s">
+        <v>385</v>
+      </c>
+      <c r="I36" t="s">
+        <v>386</v>
+      </c>
+      <c r="J36" t="s">
+        <v>387</v>
+      </c>
+      <c r="K36" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>389</v>
+      </c>
+      <c r="B37" t="s">
+        <v>390</v>
+      </c>
+      <c r="C37" t="s">
+        <v>391</v>
+      </c>
+      <c r="D37" t="s">
+        <v>392</v>
+      </c>
+      <c r="E37" t="s">
+        <v>393</v>
+      </c>
+      <c r="F37" t="s">
+        <v>394</v>
+      </c>
+      <c r="G37" t="s">
+        <v>395</v>
+      </c>
+      <c r="H37" t="s">
+        <v>396</v>
+      </c>
+      <c r="I37" t="s">
+        <v>397</v>
+      </c>
+      <c r="J37" t="s">
+        <v>398</v>
+      </c>
+      <c r="K37" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>400</v>
+      </c>
+      <c r="B38" t="s">
+        <v>401</v>
+      </c>
+      <c r="C38" t="s">
+        <v>402</v>
+      </c>
+      <c r="D38" t="s">
+        <v>403</v>
+      </c>
+      <c r="E38" t="s">
+        <v>404</v>
+      </c>
+      <c r="F38" t="s">
+        <v>405</v>
+      </c>
+      <c r="G38" t="s">
+        <v>406</v>
+      </c>
+      <c r="H38" t="s">
+        <v>407</v>
+      </c>
+      <c r="I38" t="s">
+        <v>408</v>
+      </c>
+      <c r="J38" t="s">
+        <v>409</v>
+      </c>
+      <c r="K38" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>411</v>
+      </c>
+      <c r="B39" t="s">
+        <v>412</v>
+      </c>
+      <c r="C39" t="s">
+        <v>413</v>
+      </c>
+      <c r="D39" t="s">
+        <v>414</v>
+      </c>
+      <c r="E39" t="s">
+        <v>415</v>
+      </c>
+      <c r="F39" t="s">
+        <v>416</v>
+      </c>
+      <c r="G39" t="s">
+        <v>417</v>
+      </c>
+      <c r="H39" t="s">
+        <v>418</v>
+      </c>
+      <c r="I39" t="s">
+        <v>419</v>
+      </c>
+      <c r="J39" t="s">
+        <v>420</v>
+      </c>
+      <c r="K39" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>422</v>
+      </c>
+      <c r="B40" t="s">
+        <v>423</v>
+      </c>
+      <c r="C40" t="s">
+        <v>424</v>
+      </c>
+      <c r="D40" t="s">
+        <v>425</v>
+      </c>
+      <c r="E40" t="s">
+        <v>426</v>
+      </c>
+      <c r="F40" t="s">
+        <v>427</v>
+      </c>
+      <c r="G40" t="s">
+        <v>428</v>
+      </c>
+      <c r="H40" t="s">
+        <v>429</v>
+      </c>
+      <c r="I40" t="s">
+        <v>430</v>
+      </c>
+      <c r="J40" t="s">
+        <v>431</v>
+      </c>
+      <c r="K40" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>433</v>
+      </c>
+      <c r="B41" t="s">
+        <v>434</v>
+      </c>
+      <c r="C41" t="s">
+        <v>435</v>
+      </c>
+      <c r="D41" t="s">
+        <v>436</v>
+      </c>
+      <c r="E41" t="s">
+        <v>188</v>
+      </c>
+      <c r="F41" t="s">
+        <v>437</v>
+      </c>
+      <c r="G41" t="s">
+        <v>190</v>
+      </c>
+      <c r="H41" t="s">
+        <v>438</v>
+      </c>
+      <c r="I41" t="s">
+        <v>439</v>
+      </c>
+      <c r="J41" t="s">
+        <v>440</v>
+      </c>
+      <c r="K41" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>442</v>
+      </c>
+      <c r="B42" t="s">
+        <v>443</v>
+      </c>
+      <c r="C42" t="s">
+        <v>444</v>
+      </c>
+      <c r="D42" t="s">
+        <v>445</v>
+      </c>
+      <c r="E42" t="s">
+        <v>446</v>
+      </c>
+      <c r="F42" t="s">
+        <v>447</v>
+      </c>
+      <c r="G42" t="s">
+        <v>448</v>
+      </c>
+      <c r="H42" t="s">
+        <v>449</v>
+      </c>
+      <c r="I42" t="s">
+        <v>450</v>
+      </c>
+      <c r="J42" t="s">
+        <v>451</v>
+      </c>
+      <c r="K42" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>453</v>
+      </c>
+      <c r="B43" t="s">
+        <v>454</v>
+      </c>
+      <c r="C43" t="s">
+        <v>455</v>
+      </c>
+      <c r="D43" t="s">
+        <v>456</v>
+      </c>
+      <c r="E43" t="s">
+        <v>457</v>
+      </c>
+      <c r="F43" t="s">
+        <v>458</v>
+      </c>
+      <c r="G43" t="s">
+        <v>459</v>
+      </c>
+      <c r="H43" t="s">
+        <v>460</v>
+      </c>
+      <c r="I43" t="s">
+        <v>461</v>
+      </c>
+      <c r="J43" t="s">
+        <v>462</v>
+      </c>
+      <c r="K43" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>464</v>
+      </c>
+      <c r="B44" t="s">
+        <v>465</v>
+      </c>
+      <c r="C44" t="s">
+        <v>466</v>
+      </c>
+      <c r="D44" t="s">
+        <v>467</v>
+      </c>
+      <c r="E44" t="s">
+        <v>468</v>
+      </c>
+      <c r="F44" t="s">
+        <v>469</v>
+      </c>
+      <c r="G44" t="s">
+        <v>470</v>
+      </c>
+      <c r="H44" t="s">
+        <v>471</v>
+      </c>
+      <c r="I44" t="s">
+        <v>472</v>
+      </c>
+      <c r="J44" t="s">
+        <v>473</v>
+      </c>
+      <c r="K44" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>475</v>
+      </c>
+      <c r="B45" t="s">
+        <v>476</v>
+      </c>
+      <c r="C45" t="s">
+        <v>477</v>
+      </c>
+      <c r="D45" t="s">
+        <v>478</v>
+      </c>
+      <c r="E45" t="s">
+        <v>188</v>
+      </c>
+      <c r="F45" t="s">
+        <v>479</v>
+      </c>
+      <c r="G45" t="s">
+        <v>480</v>
+      </c>
+      <c r="H45" t="s">
+        <v>481</v>
+      </c>
+      <c r="I45" t="s">
+        <v>482</v>
+      </c>
+      <c r="J45" t="s">
+        <v>483</v>
+      </c>
+      <c r="K45" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>485</v>
+      </c>
+      <c r="B46" t="s">
+        <v>486</v>
+      </c>
+      <c r="C46" t="s">
+        <v>487</v>
+      </c>
+      <c r="D46" t="s">
+        <v>488</v>
+      </c>
+      <c r="E46" t="s">
+        <v>489</v>
+      </c>
+      <c r="F46" t="s">
+        <v>490</v>
+      </c>
+      <c r="G46" t="s">
+        <v>491</v>
+      </c>
+      <c r="H46" t="s">
+        <v>492</v>
+      </c>
+      <c r="I46" t="s">
+        <v>493</v>
+      </c>
+      <c r="J46" t="s">
+        <v>494</v>
+      </c>
+      <c r="K46" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>496</v>
+      </c>
+      <c r="B47" t="s">
+        <v>497</v>
+      </c>
+      <c r="C47" t="s">
+        <v>498</v>
+      </c>
+      <c r="D47" t="s">
+        <v>499</v>
+      </c>
+      <c r="E47" t="s">
+        <v>500</v>
+      </c>
+      <c r="F47" t="s">
+        <v>501</v>
+      </c>
+      <c r="G47" t="s">
+        <v>502</v>
+      </c>
+      <c r="H47" t="s">
+        <v>503</v>
+      </c>
+      <c r="I47" t="s">
+        <v>504</v>
+      </c>
+      <c r="J47" t="s">
+        <v>505</v>
+      </c>
+      <c r="K47" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>507</v>
+      </c>
+      <c r="B48" t="s">
+        <v>508</v>
+      </c>
+      <c r="C48" t="s">
+        <v>509</v>
+      </c>
+      <c r="D48" t="s">
+        <v>510</v>
+      </c>
+      <c r="E48" t="s">
+        <v>511</v>
+      </c>
+      <c r="F48" t="s">
+        <v>512</v>
+      </c>
+      <c r="G48" t="s">
+        <v>513</v>
+      </c>
+      <c r="H48" t="s">
+        <v>514</v>
+      </c>
+      <c r="I48" t="s">
+        <v>515</v>
+      </c>
+      <c r="J48" t="s">
+        <v>516</v>
+      </c>
+      <c r="K48" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>518</v>
+      </c>
+      <c r="B49" t="s">
+        <v>519</v>
+      </c>
+      <c r="C49" t="s">
+        <v>520</v>
+      </c>
+      <c r="D49" t="s">
+        <v>521</v>
+      </c>
+      <c r="E49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F49" t="s">
+        <v>523</v>
+      </c>
+      <c r="G49" t="s">
+        <v>524</v>
+      </c>
+      <c r="H49" t="s">
+        <v>525</v>
+      </c>
+      <c r="I49" t="s">
+        <v>526</v>
+      </c>
+      <c r="J49" t="s">
+        <v>527</v>
+      </c>
+      <c r="K49" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>529</v>
+      </c>
+      <c r="B50" t="s">
+        <v>530</v>
+      </c>
+      <c r="C50" t="s">
+        <v>531</v>
+      </c>
+      <c r="D50" t="s">
+        <v>532</v>
+      </c>
+      <c r="E50" t="s">
+        <v>533</v>
+      </c>
+      <c r="F50" t="s">
+        <v>534</v>
+      </c>
+      <c r="G50" t="s">
+        <v>535</v>
+      </c>
+      <c r="H50" t="s">
+        <v>536</v>
+      </c>
+      <c r="I50" t="s">
+        <v>537</v>
+      </c>
+      <c r="J50" t="s">
+        <v>538</v>
+      </c>
+      <c r="K50" t="s">
+        <v>539</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>